--- a/toy_models/farm_toy_v7_labour.xlsx
+++ b/toy_models/farm_toy_v7_labour.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A222"/>
+  <dimension ref="A1:A242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-08-30 19:56   (from source at commit 369f0d2)</t>
+          <t>BUILT 2026-08-30 20:30   (from source at commit e35ca18)</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     profit $1,654,922 -&gt; $389,170        net margin 20.4%</t>
+          <t xml:space="preserve">     profit $1,654,922 -&gt; $388,786        net margin 20.3%</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net margin 20.4% is finally in the same postcode as a real diversified-veg farm (5-15%),</t>
+          <t>Net margin 20.3% is finally in the same postcode as a real diversified-veg farm (5-15%),</t>
         </is>
       </c>
     </row>
@@ -830,21 +830,21 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WHAT v6 ADDED — real costs, and the cash floor</t>
+          <t>INTEREST IS REPORTED, NOT OPTIMISED OVER</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>These are one job, not two. A cash curve is meaningless without costs to spend, and v5's</t>
+          <t>Peak borrowing $46,095, interest $384 — APR on the AVERAGE amount the credit line</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>profit was absurd precisely because seed was the only cost it charged.</t>
+          <t>carries, which is the app's own post-solve formula.</t>
         </is>
       </c>
     </row>
@@ -854,172 +854,180 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TIMED variable costs   seed in the PLANTING week; fertiliser and fuel every week in the</t>
+          <t>It sits OUTSIDE the objective deliberately, because that is what the app does: the plan is</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         ground at that phase's rate; packaging per lb in the week of SALE.</t>
+          <t>chosen first and the borrowing it implies is priced afterwards. The consequence is worth</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         Timing is the whole point — a cash floor cannot be honest if the</t>
+          <t>knowing — the solver has no reason to shift sales earlier to borrow less, so interest is a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         costs land in the wrong week.</t>
+          <t>REPORT here rather than a lever. On this farm it is trivial ($384); on a farm that</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FIXED costs            cooler and barn depreciation, irrigation, machinery, equipment</t>
+          <t>borrows through a long winter it would not be.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         store: $1,414 a week, owed whether or not you plant anything.</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OVERHEAD               a share of revenue, exactly as the app internalises it.</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>INTEREST IS REPORTED, NOT OPTIMISED OVER</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CASH FLOOR             cumulative cash may go negative — that is the credit line being</t>
+          <t>Peak borrowing $46,095, interest $384 — small here, and the reason is worth knowing.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">                         drawn — but never below -(opening cash + credit line). The app's C13.</t>
+          <t>The plan is chosen FIRST and the borrowing it implies is priced afterwards, so the solver has</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>no reason to shift sales earlier to borrow less. That is the app's own simplification and the</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Profit falls $2,384,231 -&gt; $389,170 once those are charged.</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>toy inherits it deliberately rather than diverging: a toy that models cash better than the</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>thing it is checking cannot check it.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>!! AND IT IS STILL ABSURD: net margin 20.4%, against 5-15% for real diversified veg.</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Because LABOUR IS NOT HERE. On the real farm wages are about 90% of fixed cost — the app's</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>WHAT v6 ADDED — real costs, and the cash floor</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>own demo pays $855,150 a year against the $73,514 of fixed cost this sheet charges. So:</t>
+          <t>These are one job, not two. A cash curve is meaningless without costs to spend, and v5's</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>profit was absurd precisely because seed was the only cost it charged.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     THE CASH FLOOR BARELY BINDS, AND YOU SHOULD NOT TRUST THIS CURVE YET.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TIMED variable costs   seed in the PLANTING week; fertiliser and fuel every week in the</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Measured: at 50,000 opening and a 250,000 credit line the floor never touches. It only bites</t>
+          <t xml:space="preserve">                         ground at that phase's rate; packaging per lb in the week of SALE.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>at about 10,000 + 10,000. The mechanism is real and checked; the farm it is checking is not</t>
+          <t xml:space="preserve">                         Timing is the whole point — a cash floor cannot be honest if the</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yet paying anybody. Labour is v7, and it is what makes cash mean something.</t>
+          <t xml:space="preserve">                         costs land in the wrong week.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FIXED costs            cooler and barn depreciation, irrigation, machinery, equipment</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>WHAT v5 ADDED — both of these you spotted missing from v4</t>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                         store: $1,414 a week, owed whether or not you plant anything.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERHEAD               a share of revenue, exactly as the app internalises it.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>1. IT CHOOSES WHEN TO PLANT.</t>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CASH FLOOR             cumulative cash may go negative — that is the credit line being</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">   All 68 plantings the app's calendar generator offers are on the sheet, one row per legal</t>
+          <t xml:space="preserve">                         drawn — but never below -(opening cash + credit line). The app's C13.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   start week. The solver puts acres on some and zero on others — and zero acres IS the</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   decision not to plant that week. v4 offered five that I picked by hand.</t>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Profit falls $2,384,231 -&gt; $388,786 once those are charged.</t>
         </is>
       </c>
     </row>
@@ -1027,106 +1035,98 @@
       <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>2. IT CHOOSES WHETHER TO PLANT AT ALL.</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>!! AND IT IS STILL ABSURD: net margin 20.3%, against 5-15% for real diversified veg.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The BLUE column is a binary per planting, tied to the acres by two constraints that are</t>
+          <t>Because LABOUR IS NOT HERE. On the real farm wages are about 90% of fixed cost — the app's</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the app's own C9 and C10:</t>
+          <t>own demo pays $855,150 a year against the $73,514 of fixed cost this sheet charges. So:</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        acres &lt;= 'max if planted'   you cannot plant acres without deciding to plant</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        acres &gt;= 'min if planted'   if you plant at all, you plant a real block</t>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     THE CASH FLOOR BARELY BINDS, AND YOU SHOULD NOT TRUST THIS CURVE YET.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   That is what stops it planting a third of an acre, and it makes this a MILP — which is</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">   what farm_v2/solver.py is. Its `integrality` array marks the very same y block.</t>
+          <t>Measured: at 50,000 opening and a 250,000 credit line the floor never touches. It only bites</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>at about 10,000 + 10,000. The mechanism is real and checked; the farm it is checking is not</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>WHAT THE TWO CHANGES ARE WORTH — measured, and they pull OPPOSITE ways</t>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>yet paying anybody. Labour is v7, and it is what makes cash mean something.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     v4, five hand-picked plantings          $1,094,831</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     v5 without the minimum-acreage rule     $404,637   (39 plantings)</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>WHAT v5 ADDED — both of these you spotted missing from v4</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     v5 as it ships                          $389,170   (31 plantings)</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>1. IT CHOOSES WHEN TO PLANT.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Letting it choose the weeks more than doubles profit. Then the minimum-acreage rule takes</t>
+          <t xml:space="preserve">   All 68 plantings the app's calendar generator offers are on the sheet, one row per legal</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>$15,466 back and drops the plan from 39 plantings to 31, because the</t>
+          <t xml:space="preserve">   start week. The solver puts acres on some and zero on others — and zero acres IS the</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>slivers are gone.</t>
+          <t xml:space="preserve">   decision not to plant that week. v4 offered five that I picked by hand.</t>
         </is>
       </c>
     </row>
@@ -1134,102 +1134,106 @@
       <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Neither number means anything alone. A fixed calendar UNDERSTATES; a missing minimum</t>
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2. IT CHOOSES WHETHER TO PLANT AT ALL.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>acreage OVERSTATES. That is why the real model has both, and it is the reason it is a MILP</t>
+          <t xml:space="preserve">   The BLUE column is a binary per planting, tied to the acres by two constraints that are</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rather than a plain LP.</t>
+          <t xml:space="preserve">   the app's own C9 and C10:</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        acres &lt;= 'max if planted'   you cannot plant acres without deciding to plant</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>WHY IT PLANTS SO MANY — this is the finding worth keeping</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        acres &gt;= 'min if planted'   if you plant at all, you plant a real block</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>31 plantings out of 68, staggered across the season rather than a few big</t>
+          <t xml:space="preserve">   That is what stops it planting a third of an acre, and it makes this a MILP — which is</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>blocks. That is SUCCESSION PLANTING, and now you can see why it pays: spreading the harvest</t>
+          <t xml:space="preserve">   what farm_v2/solver.py is. Its `integrality` array marks the very same y block.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>is what lets you serve a WEEKLY demand cap continuously. Plant it all at once and one huge</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>harvest slams into the ceiling, the cooler fills, and the surplus is wasted or dumped cheap.</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE TWO CHANGES ARE WORTH — measured, and they pull OPPOSITE ways</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     v4, five hand-picked plantings          $1,094,831</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A model with a fixed planting calendar cannot express the thing the practice exists for.</t>
+          <t xml:space="preserve">     v5 without the minimum-acreage rule     $404,238   (39 plantings)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     v5 as it ships                          $388,786   (31 plantings)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>!! IT NEEDS LIBREOFFICE, AND THIS ONE IS A REAL MILP</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>448 decision cells: 68 acres + 68 binaries + 312 offered. The engine MUST be</t>
+          <t>Letting it choose the weeks more than doubles profit. Then the minimum-acreage rule takes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CoinMP — it does branch and bound over the integers. Expect it to take appreciably longer</t>
+          <t>$15,452 back and drops the plan from 39 plantings to 31, because the</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>than v4; integers are what make an optimizer work for its living.</t>
+          <t>slivers are gone.</t>
         </is>
       </c>
     </row>
@@ -1237,306 +1241,310 @@
       <c r="A107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>WHERE THINGS ARE</t>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Neither number means anything alone. A fixed calendar UNDERSTATES; a missing minimum</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">  YELLOW   you type: the farm, the crop table, the crop x channel table.</t>
+          <t>acreage OVERSTATES. That is why the real model has both, and it is the reason it is a MILP</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GREEN    the solver writes: the ACRES column (C38:C105), the six OFFERED rows, and</t>
+          <t>rather than a plain LP.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           the PROFIT cell (B257).</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BLUE     the solver writes: the PLANT? binaries (D38:D105).</t>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>WHY IT PLANTS SO MANY — this is the finding worth keeping</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Everything else is a formula. Columns A-D stay put when you scroll right.</t>
+          <t>31 plantings out of 68, staggered across the season rather than a few big</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>blocks. That is SUCCESSION PLANTING, and now you can see why it pays: spreading the harvest</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>HOW TO RUN IT</t>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>is what lets you serve a WEEKLY demand cap continuously. Plant it all at once and one huge</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Section 7 lists every entry with exact ranges. In short:</t>
+          <t>harvest slams into the ceiling, the cooler fills, and the surplus is wasted or dumped cheap.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tools &gt; Solver, target the PROFIT cell, set to MAXIMUM</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Changing cells: C38:C105 and D38:D105 together, plus the six OFFERED rows</t>
+          <t>A model with a fixed planting calendar cannot express the thing the practice exists for.</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Add the constraint  D38:D105 = Binary   — without it the binaries are just numbers</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   and the minimum-acreage rule silently stops working</t>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>!! IT NEEDS LIBREOFFICE, AND THIS ONE IS A REAL MILP</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Options: engine = LibreOffice CoinMP Linear Solver; tick non-negative</t>
+          <t>448 decision cells: 68 acres + 68 binaries + 312 offered. The engine MUST be</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CoinMP — it does branch and bound over the integers. Expect it to take appreciably longer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IT SHOULD FIND</t>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>than v4; integers are what make an optimizer work for its living.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     PROFIT   $389,170       net margin 20.4%</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       revenue      $1,912,071</t>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>WHERE THINGS ARE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">       growing      $141,302      seed at planting + fertiliser and fuel in the ground</t>
+          <t xml:space="preserve">  YELLOW   you type: the farm, the crop table, the crop x channel table.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">       packaging    $147,003      per lb sold, in the week of sale</t>
+          <t xml:space="preserve">  GREEN    the solver writes: the ACRES column (C38:C105), the six OFFERED rows, and</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">       fixed        $73,514      $1,414 a week, owed whether or not you plant</t>
+          <t xml:space="preserve">           the PROFIT cell (B262).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">       overhead     $305,931      a share of revenue</t>
+          <t xml:space="preserve">  BLUE     the solver writes: the PLANT? binaries (D38:D105).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">       wages        $855,150      committed — owed whether the crops need the hours or not</t>
+          <t xml:space="preserve">  Everything else is a formula. Columns A-D stay put when you scroll right.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     31 of 68 plantings used</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO RUN IT</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Computed by solving the same MILP with scipy.milp — the same HiGHS solver your app runs. A</t>
+          <t>Section 7 lists every entry with exact ranges. In short:</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>few dollars apart is tolerances. Materially different means one of the two models is not the</t>
+          <t xml:space="preserve">   Tools &gt; Solver, target the PROFIT cell, set to MAXIMUM</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>model we think it is.</t>
+          <t xml:space="preserve">   Changing cells: C38:C105 and D38:D105 together, plus the six OFFERED rows</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Add the constraint  D38:D105 = Binary   — without it the binaries are just numbers</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>WHAT SELL-THROUGH IS, AND WHY IT SHIPS AT 1.00</t>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   and the minimum-acreage rule silently stops working</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Every 'Sell-through' in section 3 is 1.00, matching the app since 30 Aug. The 85% it used to</t>
+          <t xml:space="preserve">   Options: engine = LibreOffice CoinMP Linear Solver; tick non-negative</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>carry had no source, and it was being charged on channels where a purchase order exists and</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>nothing goes unsold. So the market-loss and returned-to-store rows all read ZERO right now.</t>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IT SHOULD FIND</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>That is correct, not broken.</t>
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     PROFIT   $388,786       net margin 20.3%</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       revenue      $1,912,071</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>The narrow definition it now carries:</t>
+          <t xml:space="preserve">       growing      $141,302      seed at planting + fertiliser and fuel in the ground</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       packaging    $147,003      per lb sold, in the week of sale</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Of what you TAKE TO MARKET, the share that converts to cash — display attrition at a</t>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       fixed        $73,514      $1,414 a week, owed whether or not you plant</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     stall, samples, transit damage, a rejected load.</t>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       overhead     $305,931      a share of revenue</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       wages        $855,150      committed — owed whether the crops need the hours or not</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NOT grade-out at harvest (that is pack-out, above the store). NOT spoilage in the store (that</t>
+          <t xml:space="preserve">       interest     $384          APR on what the credit line actually carries</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>is shrink). And NOT demand uncertainty — which is the one worth understanding, because it is</t>
+          <t xml:space="preserve">     peak borrowing $46,095 — the deepest the line is ever drawn</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>why the old wording could not be right:</t>
+          <t xml:space="preserve">       interest     $384          on $46,095 of peak borrowing — reported, not optimised over</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     31 of 68 plantings used</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     The demand ceiling is HARD. At a 6,000 lb cap and 0.85, selling 6,000 means bringing</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">     7,059 and losing 1,059 — every week, including the best Saturday of the year, because</t>
+          <t>Computed by solving the same MILP with scipy.milp — the same HiGHS solver your app runs. A</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the model will never let you sell 6,001. That is the whole downside of bringing extra</t>
+          <t>few dollars apart is tolerances. Materially different means one of the two models is not the</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">     with none of the upside. It is not a model of uncertainty; it is a one-sided penalty.</t>
+          <t>model we think it is.</t>
         </is>
       </c>
     </row>
@@ -1544,158 +1552,150 @@
       <c r="A156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>So what it CAN mean is a display requirement: a picked-over stall sells less than a full one,</t>
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>WHAT SELL-THROUGH IS, AND WHY IT SHIPS AT 1.00</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>so moving 6,000 lb needs more than 6,000 lb on the table. Deterministic, and an input</t>
+          <t>Every 'Sell-through' in section 3 is 1.00, matching the app since 30 Aug. The 85% it used to</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>requirement like seed. Real demand variance is a different problem (newsvendor) needing</t>
+          <t>carry had no source, and it was being charged on channels where a purchase order exists and</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>machinery neither this sheet nor the app has yet.</t>
+          <t>nothing goes unsold. So the market-loss and returned-to-store rows all read ZERO right now.</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>That is correct, not broken.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>THREE THINGS TO TRY</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>The narrow definition it now carries:</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 1 — switch sell-through on, and watch the crop decide what happens.</t>
-        </is>
-      </c>
+      <c r="A164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In section 3 set Spinach / {CH1} sell-through to 0.85, and Garlic / {CH1} to 0.85 too.</t>
+          <t xml:space="preserve">     Of what you TAKE TO MARKET, the share that converts to cash — display attrition at a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Re-solve.</t>
+          <t xml:space="preserve">     stall, samples, transit damage, a rejected load.</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Both now offer more than they sell. But look at the two 'market loss' rows: Spinach's is</t>
-        </is>
-      </c>
+      <c r="A167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">   positive and Garlic's is ZERO, because garlic's 'Returns to store' is 1.00 — unsold garlic</t>
+          <t>NOT grade-out at harvest (that is pack-out, above the store). NOT spoilage in the store (that</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">   comes home and sells later, so the loss is a DELAY, not a loss.</t>
+          <t>is shrink). And NOT demand uncertainty — which is the one worth understanding, because it is</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">   That is the grower's ruling in two cells: the same sell-through means different things on</t>
+          <t>why the old wording could not be right:</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   different crops, which is why it belongs on the crop x channel row and not on either one</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">   alone. Now set Garlic's 'Returns to store' to 0.00 and re-solve: the delay becomes a loss</t>
+          <t xml:space="preserve">     The demand ceiling is HARD. At a 6,000 lb cap and 0.85, selling 6,000 means bringing</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and the plan changes.</t>
+          <t xml:space="preserve">     7,059 and losing 1,059 — every week, including the best Saturday of the year, because</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     the model will never let you sell 6,001. That is the whole downside of bringing extra</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 2 — sack the harvest crew.  Set the Harvest Crew count to 0 and re-solve.</t>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     with none of the upside. It is not a model of uncertainty; it is a one-sided penalty.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   You save their whole wage bill. Watch what happens to profit anyway: with fewer hours in</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">   weeks 14-40 the crops that need picking most cannot be picked, and revenue falls further</t>
+          <t>So what it CAN mean is a display requirement: a picked-over stall sells less than a full one,</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">   than the wages saved. Then try the opposite — double their count — and watch profit rise</t>
+          <t>so moving 6,000 lb needs more than 6,000 lb on the table. Deterministic, and an input</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">   even though payroll rose too. That is the trade a per-acre labour charge cannot express,</t>
+          <t>requirement like seed. Real demand variance is a different problem (newsvendor) needing</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and it is why the app rations hours with a constraint rather than pricing them.</t>
+          <t>machinery neither this sheet nor the app has yet.</t>
         </is>
       </c>
     </row>
@@ -1703,127 +1703,127 @@
       <c r="A181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 3 — squeeze the cash.  Set the credit line to 10,000 and opening cash to 10,000,</t>
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>THREE THINGS TO TRY</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   then re-solve.</t>
-        </is>
-      </c>
+      <c r="A183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Below about $100,000 combined there is no feasible plan at all — see above. Just above</t>
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 1 — switch sell-through on, and watch the crop decide what happens.</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   it, watch WHICH plantings the floor drops: not the least profitable ones, but</t>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   In section 3 set Spinach / {CH1} sell-through to 0.85, and Garlic / {CH1} to 0.85 too.</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the ones whose costs land earliest relative to their revenue. Garlic goes in around week</t>
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Re-solve.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 and is not sold until week 30 of the following year — nine months of money out before</t>
+          <t xml:space="preserve">   Both now offer more than they sell. But look at the two 'market loss' rows: Spinach's is</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">   a dollar comes back. Cash does not rank crops by margin; it ranks them by TIMING, which no</t>
+          <t xml:space="preserve">   positive and Garlic's is ZERO, because garlic's 'Returns to store' is 1.00 — unsold garlic</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">   column on this sheet shows you.</t>
+          <t xml:space="preserve">   comes home and sells later, so the loss is a DELAY, not a loss.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   That is the grower's ruling in two cells: the same sell-through means different things on</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 4 — drop the minimum acreage.  Set every 'Min acres if planted' in the crop</t>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   different crops, which is why it belongs on the crop x channel row and not on either one</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   table to 0 and re-solve.</t>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   alone. Now set Garlic's 'Returns to store' to 0.00 and re-solve: the delay becomes a loss</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Expect $404,637 and 39 plantings. The extra profit is real but the plan is</t>
+          <t xml:space="preserve">   and the plan changes.</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   not: it plants fractions of an acre no one would drive a tractor out for. This is what</t>
-        </is>
-      </c>
+      <c r="A194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 2 — sack the harvest crew.  Set the Harvest Crew count to 0 and re-solve.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   You save their whole wage bill. Watch what happens to profit anyway: with fewer hours in</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 5 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   weeks 14-40 the crops that need picking most cannot be picked, and revenue falls further</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Watch WHICH WEEKS it abandons, not just which crop. With a full calendar it can retreat</t>
+          <t xml:space="preserve">   than the wages saved. Then try the opposite — double their count — and watch profit rise</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">   to a planting pattern that keeps the cooler under its ceiling — an answer v4 could not</t>
+          <t xml:space="preserve">   even though payroll rose too. That is the trade a per-acre labour charge cannot express,</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">   even represent.</t>
+          <t xml:space="preserve">   and it is why the app rations hours with a constraint rather than pricing them.</t>
         </is>
       </c>
     </row>
@@ -1831,58 +1831,58 @@
       <c r="A201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>WHAT v5 STILL DOES NOT CARRY</t>
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 3 — squeeze the cash.  Set the credit line to 10,000 and opening cash to 10,000,</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   then re-solve.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
+          <t xml:space="preserve">   Below about $100,000 combined there is no feasible plan at all — see above. Just above</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+          <t xml:space="preserve">   it, watch WHICH plantings the floor drops: not the least profitable ones, but</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Shelf life IS enforced now (a real constraint since you found it dead). Shrink is wired</t>
+          <t xml:space="preserve">   the ones whose costs land earliest relative to their revenue. Garlic goes in around week</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">    too, but defaults to 0%, so it stays invisible until you set it.</t>
+          <t xml:space="preserve">   47 and is not sold until week 30 of the following year — nine months of money out before</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
+          <t xml:space="preserve">   a dollar comes back. Cash does not rank crops by margin; it ranks them by TIMING, which no</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Three crops, not seven.</t>
+          <t xml:space="preserve">   column on this sheet shows you.</t>
         </is>
       </c>
     </row>
@@ -1890,80 +1890,208 @@
       <c r="A210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>!! THE SCALE WARNING</t>
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 4 — drop the minimum acreage.  Set every 'Min acres if planted' in the crop</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>An optimizer's answer is far more scale-sensitive than a calculator's: which constraint binds,</t>
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   table to 0 and re-solve.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>and therefore which crop and which WEEK wins, can invert between 3 crops and 7. This teaches</t>
+          <t xml:space="preserve">   Expect $404,238 and 39 plantings. The extra profit is real but the plan is</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>the machinery. It is not advice about your farm.</t>
+          <t xml:space="preserve">   not: it plants fractions of an acre no one would drive a tractor out for. This is what</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>HAS THIS SHEET BEEN CHECKED?</t>
-        </is>
-      </c>
+      <c r="A216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 5 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
+          <t xml:space="preserve">   Watch WHICH WEEKS it abandons, not just which crop. With a full calendar it can retreat</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+          <t xml:space="preserve">   to a planting pattern that keeps the cooler under its ceiling — an answer v4 could not</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
+          <t xml:space="preserve">   even represent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>WHAT v5 STILL DOES NOT CARRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Shelf life IS enforced now (a real constraint since you found it dead). Shrink is wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    too, but defaults to 0%, so it stays invisible until you set it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Three crops, not seven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>!! THE SCALE WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>An optimizer's answer is far more scale-sensitive than a calculator's: which constraint binds,</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>and therefore which crop and which WEEK wins, can invert between 3 crops and 7. This teaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>the machinery. It is not advice about your farm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>HAS THIS SHEET BEEN CHECKED?</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
           <t>same MILP is solved with scipy.milp, its answer written into the decision cells, and the</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>sheet's own PROFIT cell must reproduce the optimum exactly.</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t xml:space="preserve">     Run it yourself:   .venv/bin/python toy_models/verify_toy_v7.py</t>
         </is>
@@ -1980,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG287"/>
+  <dimension ref="A1:BG292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2052,7 +2180,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-08-30 19:56   (from source at 369f0d2)</t>
+          <t>BUILT 2026-08-30 20:30   (from source at e35ca18)</t>
         </is>
       </c>
     </row>
@@ -2188,6 +2316,21 @@
           <t>$/ac harvest wk</t>
         </is>
       </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>hrs/ac plant</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>hrs/ac grow</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>hrs/ac harvest</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -2234,6 +2377,15 @@
       <c r="M11" s="16" t="n">
         <v>11.285</v>
       </c>
+      <c r="N11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -2280,6 +2432,15 @@
       <c r="M12" s="16" t="n">
         <v>10.08</v>
       </c>
+      <c r="N12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -2326,6 +2487,15 @@
       <c r="M13" s="16" t="n">
         <v>19.75</v>
       </c>
+      <c r="N13" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2801,7 +2971,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>employer taxes, workers' comp, benefits — on top of every wage</t>
+          <t>employer taxes, workers' comp, benefits — applied to EVERY wage, salaried included</t>
         </is>
       </c>
     </row>
@@ -10456,211 +10626,211 @@
         </is>
       </c>
       <c r="E117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=1)*($H$27:$H$30&gt;=1)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=1)*($H$27:$H$30&gt;=1)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="F117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=2)*($H$27:$H$30&gt;=2)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=2)*($H$27:$H$30&gt;=2)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="G117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=3)*($H$27:$H$30&gt;=3)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=3)*($H$27:$H$30&gt;=3)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="H117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=4)*($H$27:$H$30&gt;=4)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=4)*($H$27:$H$30&gt;=4)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="I117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=5)*($H$27:$H$30&gt;=5)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=5)*($H$27:$H$30&gt;=5)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="J117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=6)*($H$27:$H$30&gt;=6)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=6)*($H$27:$H$30&gt;=6)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="K117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=7)*($H$27:$H$30&gt;=7)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=7)*($H$27:$H$30&gt;=7)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="L117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=8)*($H$27:$H$30&gt;=8)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=8)*($H$27:$H$30&gt;=8)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="M117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=9)*($H$27:$H$30&gt;=9)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=9)*($H$27:$H$30&gt;=9)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="N117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=10)*($H$27:$H$30&gt;=10)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=10)*($H$27:$H$30&gt;=10)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="O117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=11)*($H$27:$H$30&gt;=11)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=11)*($H$27:$H$30&gt;=11)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="P117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=12)*($H$27:$H$30&gt;=12)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=12)*($H$27:$H$30&gt;=12)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="Q117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=13)*($H$27:$H$30&gt;=13)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=13)*($H$27:$H$30&gt;=13)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="R117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=14)*($H$27:$H$30&gt;=14)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=14)*($H$27:$H$30&gt;=14)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="S117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=15)*($H$27:$H$30&gt;=15)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=15)*($H$27:$H$30&gt;=15)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="T117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=16)*($H$27:$H$30&gt;=16)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=16)*($H$27:$H$30&gt;=16)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="U117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=17)*($H$27:$H$30&gt;=17)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=17)*($H$27:$H$30&gt;=17)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="V117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=18)*($H$27:$H$30&gt;=18)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=18)*($H$27:$H$30&gt;=18)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="W117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=19)*($H$27:$H$30&gt;=19)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=19)*($H$27:$H$30&gt;=19)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="X117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=20)*($H$27:$H$30&gt;=20)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=20)*($H$27:$H$30&gt;=20)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="Y117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=21)*($H$27:$H$30&gt;=21)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=21)*($H$27:$H$30&gt;=21)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="Z117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=22)*($H$27:$H$30&gt;=22)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=22)*($H$27:$H$30&gt;=22)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AA117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=23)*($H$27:$H$30&gt;=23)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=23)*($H$27:$H$30&gt;=23)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AB117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=24)*($H$27:$H$30&gt;=24)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=24)*($H$27:$H$30&gt;=24)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AC117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=25)*($H$27:$H$30&gt;=25)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=25)*($H$27:$H$30&gt;=25)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AD117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=26)*($H$27:$H$30&gt;=26)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=26)*($H$27:$H$30&gt;=26)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AE117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=27)*($H$27:$H$30&gt;=27)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=27)*($H$27:$H$30&gt;=27)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AF117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=28)*($H$27:$H$30&gt;=28)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=28)*($H$27:$H$30&gt;=28)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AG117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=29)*($H$27:$H$30&gt;=29)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=29)*($H$27:$H$30&gt;=29)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AH117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=30)*($H$27:$H$30&gt;=30)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=30)*($H$27:$H$30&gt;=30)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AI117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=31)*($H$27:$H$30&gt;=31)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=31)*($H$27:$H$30&gt;=31)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AJ117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=32)*($H$27:$H$30&gt;=32)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=32)*($H$27:$H$30&gt;=32)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AK117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=33)*($H$27:$H$30&gt;=33)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=33)*($H$27:$H$30&gt;=33)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AL117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=34)*($H$27:$H$30&gt;=34)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=34)*($H$27:$H$30&gt;=34)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AM117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=35)*($H$27:$H$30&gt;=35)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=35)*($H$27:$H$30&gt;=35)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AN117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=36)*($H$27:$H$30&gt;=36)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=36)*($H$27:$H$30&gt;=36)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AO117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=37)*($H$27:$H$30&gt;=37)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=37)*($H$27:$H$30&gt;=37)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AP117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=38)*($H$27:$H$30&gt;=38)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=38)*($H$27:$H$30&gt;=38)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AQ117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=39)*($H$27:$H$30&gt;=39)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=39)*($H$27:$H$30&gt;=39)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AR117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=40)*($H$27:$H$30&gt;=40)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=40)*($H$27:$H$30&gt;=40)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AS117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=41)*($H$27:$H$30&gt;=41)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=41)*($H$27:$H$30&gt;=41)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AT117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=42)*($H$27:$H$30&gt;=42)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=42)*($H$27:$H$30&gt;=42)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AU117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=43)*($H$27:$H$30&gt;=43)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=43)*($H$27:$H$30&gt;=43)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AV117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=44)*($H$27:$H$30&gt;=44)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=44)*($H$27:$H$30&gt;=44)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AW117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=45)*($H$27:$H$30&gt;=45)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=45)*($H$27:$H$30&gt;=45)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AX117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=46)*($H$27:$H$30&gt;=46)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=46)*($H$27:$H$30&gt;=46)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AY117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=47)*($H$27:$H$30&gt;=47)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=47)*($H$27:$H$30&gt;=47)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="AZ117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=48)*($H$27:$H$30&gt;=48)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=48)*($H$27:$H$30&gt;=48)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="BA117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=49)*($H$27:$H$30&gt;=49)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=49)*($H$27:$H$30&gt;=49)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="BB117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=50)*($H$27:$H$30&gt;=50)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=50)*($H$27:$H$30&gt;=50)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="BC117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=51)*($H$27:$H$30&gt;=51)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=51)*($H$27:$H$30&gt;=51)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
       <c r="BD117" s="36">
-        <f>SUMPRODUCT(($G$27:$G$30&lt;=52)*($H$27:$H$30&gt;=52)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52,$D$27:$D$30*$E$27:$E$30))*(1+$B$31)</f>
+        <f>SUMPRODUCT(($G$27:$G$30&lt;=52)*($H$27:$H$30&gt;=52)*$B$27:$B$30*IF($C$27:$C$30="salary",$D$27:$D$30/52*(1+$B$31),$D$27:$D$30*$E$27:$E$30*(1+$B$31)))</f>
         <v/>
       </c>
     </row>
@@ -10851,211 +11021,211 @@
         </is>
       </c>
       <c r="E121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(E$38:E$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(E$38:E$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(E$38:E$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="F121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(F$38:F$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(F$38:F$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(F$38:F$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="G121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(G$38:G$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(G$38:G$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(G$38:G$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="H121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(H$38:H$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(H$38:H$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(H$38:H$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="I121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(I$38:I$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(I$38:I$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(I$38:I$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="J121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(J$38:J$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(J$38:J$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(J$38:J$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="K121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(K$38:K$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(K$38:K$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(K$38:K$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="L121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(L$38:L$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(L$38:L$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(L$38:L$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="M121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(M$38:M$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(M$38:M$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(M$38:M$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="N121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(N$38:N$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(N$38:N$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(N$38:N$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="O121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(O$38:O$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(O$38:O$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(O$38:O$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="P121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(P$38:P$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(P$38:P$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(P$38:P$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="Q121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Q$38:Q$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Q$38:Q$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Q$38:Q$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="R121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(R$38:R$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(R$38:R$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(R$38:R$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="S121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(S$38:S$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(S$38:S$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(S$38:S$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="T121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(T$38:T$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(T$38:T$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(T$38:T$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="U121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(U$38:U$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(U$38:U$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(U$38:U$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="V121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(V$38:V$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(V$38:V$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(V$38:V$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="W121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(W$38:W$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(W$38:W$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(W$38:W$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="X121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(X$38:X$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(X$38:X$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(X$38:X$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="Y121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Y$38:Y$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Y$38:Y$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Y$38:Y$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="Z121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(Z$38:Z$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(Z$38:Z$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(Z$38:Z$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AA121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AA$38:AA$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AA$38:AA$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AA$38:AA$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AB121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AB$38:AB$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AB$38:AB$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AB$38:AB$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AC121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AC$38:AC$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AC$38:AC$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AC$38:AC$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AD121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AD$38:AD$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AD$38:AD$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AD$38:AD$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AE121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AE$38:AE$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AE$38:AE$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AE$38:AE$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AF121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AF$38:AF$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AF$38:AF$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AF$38:AF$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AG121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AG$38:AG$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AG$38:AG$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AG$38:AG$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AH121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AH$38:AH$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AH$38:AH$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AH$38:AH$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AI121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AI$38:AI$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AI$38:AI$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AI$38:AI$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AJ121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AJ$38:AJ$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AJ$38:AJ$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AJ$38:AJ$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AK121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AK$38:AK$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AK$38:AK$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AK$38:AK$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AL121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AL$38:AL$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AL$38:AL$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AL$38:AL$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AM121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AM$38:AM$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AM$38:AM$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AM$38:AM$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AN121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AN$38:AN$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AN$38:AN$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AN$38:AN$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AO121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AO$38:AO$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AO$38:AO$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AO$38:AO$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AP121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AP$38:AP$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AP$38:AP$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AP$38:AP$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AQ121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AQ$38:AQ$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AQ$38:AQ$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AQ$38:AQ$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AR121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AR$38:AR$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AR$38:AR$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AR$38:AR$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AS121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AS$38:AS$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AS$38:AS$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AS$38:AS$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AT121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AT$38:AT$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AT$38:AT$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AT$38:AT$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AU121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AU$38:AU$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AU$38:AU$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AU$38:AU$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AV121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AV$38:AV$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AV$38:AV$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AV$38:AV$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AW121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AW$38:AW$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AW$38:AW$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AW$38:AW$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AX121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AX$38:AX$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AX$38:AX$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AX$38:AX$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AY121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AY$38:AY$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AY$38:AY$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AY$38:AY$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="AZ121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(AZ$38:AZ$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(AZ$38:AZ$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(AZ$38:AZ$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="BA121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BA$38:BA$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BA$38:BA$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BA$38:BA$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="BB121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BB$38:BB$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BB$38:BB$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BB$38:BB$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="BC121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BC$38:BC$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BC$38:BC$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BC$38:BC$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
       <c r="BD121" s="36">
-        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="P")*$C$38:$C$105)*2+SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="G")*$C$38:$C$105)*4+SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="H")*$C$38:$C$105)*50+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="P")*$C$38:$C$105)*3+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="G")*$C$38:$C$105)*2.5+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="H")*$C$38:$C$105)*22+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="P")*$C$38:$C$105)*6.7+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="G")*$C$38:$C$105)*0.3+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="H")*$C$38:$C$105)*75</f>
+        <f>SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="P")*$C$38:$C$105)*$N$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="G")*$C$38:$C$105)*$O$11+SUMPRODUCT(($B$38:$B$105="Spinach")*(BD$38:BD$105="H")*$C$38:$C$105)*$P$11+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="P")*$C$38:$C$105)*$N$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="G")*$C$38:$C$105)*$O$12+SUMPRODUCT(($B$38:$B$105="Kale")*(BD$38:BD$105="H")*$C$38:$C$105)*$P$12+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="P")*$C$38:$C$105)*$N$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="G")*$C$38:$C$105)*$O$13+SUMPRODUCT(($B$38:$B$105="Garlic")*(BD$38:BD$105="H")*$C$38:$C$105)*$P$13</f>
         <v/>
       </c>
     </row>
@@ -28163,618 +28333,413 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="22" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Interest APR on borrowing</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>charged on what the credit line actually carries — reported below, not optimised over</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B231" s="33" t="inlineStr">
+      <c r="B232" s="33" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E231" s="25" t="n">
+      <c r="E232" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F231" s="25" t="n">
+      <c r="F232" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G231" s="25" t="n">
+      <c r="G232" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H231" s="25" t="n">
+      <c r="H232" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I231" s="25" t="n">
+      <c r="I232" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J231" s="25" t="n">
+      <c r="J232" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="K231" s="25" t="n">
+      <c r="K232" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="L231" s="25" t="n">
+      <c r="L232" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="M231" s="25" t="n">
+      <c r="M232" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="N231" s="25" t="n">
+      <c r="N232" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="O231" s="25" t="n">
+      <c r="O232" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="P231" s="25" t="n">
+      <c r="P232" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="Q231" s="25" t="n">
+      <c r="Q232" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="R231" s="25" t="n">
+      <c r="R232" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="S231" s="25" t="n">
+      <c r="S232" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="T231" s="25" t="n">
+      <c r="T232" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="U231" s="25" t="n">
+      <c r="U232" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="V231" s="25" t="n">
+      <c r="V232" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="W231" s="25" t="n">
+      <c r="W232" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="X231" s="25" t="n">
+      <c r="X232" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="Y231" s="25" t="n">
+      <c r="Y232" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="Z231" s="25" t="n">
+      <c r="Z232" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="AA231" s="25" t="n">
+      <c r="AA232" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="AB231" s="25" t="n">
+      <c r="AB232" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="AC231" s="25" t="n">
+      <c r="AC232" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="AD231" s="25" t="n">
+      <c r="AD232" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="AE231" s="25" t="n">
+      <c r="AE232" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="AF231" s="25" t="n">
+      <c r="AF232" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="AG231" s="25" t="n">
+      <c r="AG232" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="AH231" s="25" t="n">
+      <c r="AH232" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="AI231" s="25" t="n">
+      <c r="AI232" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="AJ231" s="25" t="n">
+      <c r="AJ232" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="AK231" s="25" t="n">
+      <c r="AK232" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="AL231" s="25" t="n">
+      <c r="AL232" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="AM231" s="25" t="n">
+      <c r="AM232" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="AN231" s="25" t="n">
+      <c r="AN232" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="AO231" s="25" t="n">
+      <c r="AO232" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="AP231" s="25" t="n">
+      <c r="AP232" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="AQ231" s="25" t="n">
+      <c r="AQ232" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="AR231" s="25" t="n">
+      <c r="AR232" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="AS231" s="25" t="n">
+      <c r="AS232" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="AT231" s="25" t="n">
+      <c r="AT232" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="AU231" s="25" t="n">
+      <c r="AU232" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="AV231" s="25" t="n">
+      <c r="AV232" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="AW231" s="25" t="n">
+      <c r="AW232" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="AX231" s="25" t="n">
+      <c r="AX232" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="AY231" s="25" t="n">
+      <c r="AY232" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="AZ231" s="25" t="n">
+      <c r="AZ232" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="BA231" s="25" t="n">
+      <c r="BA232" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="BB231" s="25" t="n">
+      <c r="BB232" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="BC231" s="25" t="n">
+      <c r="BC232" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="BD231" s="25" t="n">
+      <c r="BD232" s="25" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E232" s="36">
+      <c r="E233" s="36">
         <f>E135*$I$18+E141*$I$19+E162*$I$20+E170*$I$21+E191*$I$22+E197*$I$23</f>
         <v/>
       </c>
-      <c r="F232" s="36">
+      <c r="F233" s="36">
         <f>F135*$I$18+F141*$I$19+F162*$I$20+F170*$I$21+F191*$I$22+F197*$I$23</f>
         <v/>
       </c>
-      <c r="G232" s="36">
+      <c r="G233" s="36">
         <f>G135*$I$18+G141*$I$19+G162*$I$20+G170*$I$21+G191*$I$22+G197*$I$23</f>
         <v/>
       </c>
-      <c r="H232" s="36">
+      <c r="H233" s="36">
         <f>H135*$I$18+H141*$I$19+H162*$I$20+H170*$I$21+H191*$I$22+H197*$I$23</f>
         <v/>
       </c>
-      <c r="I232" s="36">
+      <c r="I233" s="36">
         <f>I135*$I$18+I141*$I$19+I162*$I$20+I170*$I$21+I191*$I$22+I197*$I$23</f>
         <v/>
       </c>
-      <c r="J232" s="36">
+      <c r="J233" s="36">
         <f>J135*$I$18+J141*$I$19+J162*$I$20+J170*$I$21+J191*$I$22+J197*$I$23</f>
         <v/>
       </c>
-      <c r="K232" s="36">
+      <c r="K233" s="36">
         <f>K135*$I$18+K141*$I$19+K162*$I$20+K170*$I$21+K191*$I$22+K197*$I$23</f>
         <v/>
       </c>
-      <c r="L232" s="36">
+      <c r="L233" s="36">
         <f>L135*$I$18+L141*$I$19+L162*$I$20+L170*$I$21+L191*$I$22+L197*$I$23</f>
         <v/>
       </c>
-      <c r="M232" s="36">
+      <c r="M233" s="36">
         <f>M135*$I$18+M141*$I$19+M162*$I$20+M170*$I$21+M191*$I$22+M197*$I$23</f>
         <v/>
       </c>
-      <c r="N232" s="36">
+      <c r="N233" s="36">
         <f>N135*$I$18+N141*$I$19+N162*$I$20+N170*$I$21+N191*$I$22+N197*$I$23</f>
         <v/>
       </c>
-      <c r="O232" s="36">
+      <c r="O233" s="36">
         <f>O135*$I$18+O141*$I$19+O162*$I$20+O170*$I$21+O191*$I$22+O197*$I$23</f>
         <v/>
       </c>
-      <c r="P232" s="36">
+      <c r="P233" s="36">
         <f>P135*$I$18+P141*$I$19+P162*$I$20+P170*$I$21+P191*$I$22+P197*$I$23</f>
         <v/>
       </c>
-      <c r="Q232" s="36">
+      <c r="Q233" s="36">
         <f>Q135*$I$18+Q141*$I$19+Q162*$I$20+Q170*$I$21+Q191*$I$22+Q197*$I$23</f>
         <v/>
       </c>
-      <c r="R232" s="36">
+      <c r="R233" s="36">
         <f>R135*$I$18+R141*$I$19+R162*$I$20+R170*$I$21+R191*$I$22+R197*$I$23</f>
         <v/>
       </c>
-      <c r="S232" s="36">
+      <c r="S233" s="36">
         <f>S135*$I$18+S141*$I$19+S162*$I$20+S170*$I$21+S191*$I$22+S197*$I$23</f>
         <v/>
       </c>
-      <c r="T232" s="36">
+      <c r="T233" s="36">
         <f>T135*$I$18+T141*$I$19+T162*$I$20+T170*$I$21+T191*$I$22+T197*$I$23</f>
         <v/>
       </c>
-      <c r="U232" s="36">
+      <c r="U233" s="36">
         <f>U135*$I$18+U141*$I$19+U162*$I$20+U170*$I$21+U191*$I$22+U197*$I$23</f>
         <v/>
       </c>
-      <c r="V232" s="36">
+      <c r="V233" s="36">
         <f>V135*$I$18+V141*$I$19+V162*$I$20+V170*$I$21+V191*$I$22+V197*$I$23</f>
         <v/>
       </c>
-      <c r="W232" s="36">
+      <c r="W233" s="36">
         <f>W135*$I$18+W141*$I$19+W162*$I$20+W170*$I$21+W191*$I$22+W197*$I$23</f>
         <v/>
       </c>
-      <c r="X232" s="36">
+      <c r="X233" s="36">
         <f>X135*$I$18+X141*$I$19+X162*$I$20+X170*$I$21+X191*$I$22+X197*$I$23</f>
         <v/>
       </c>
-      <c r="Y232" s="36">
+      <c r="Y233" s="36">
         <f>Y135*$I$18+Y141*$I$19+Y162*$I$20+Y170*$I$21+Y191*$I$22+Y197*$I$23</f>
         <v/>
       </c>
-      <c r="Z232" s="36">
+      <c r="Z233" s="36">
         <f>Z135*$I$18+Z141*$I$19+Z162*$I$20+Z170*$I$21+Z191*$I$22+Z197*$I$23</f>
         <v/>
       </c>
-      <c r="AA232" s="36">
+      <c r="AA233" s="36">
         <f>AA135*$I$18+AA141*$I$19+AA162*$I$20+AA170*$I$21+AA191*$I$22+AA197*$I$23</f>
         <v/>
       </c>
-      <c r="AB232" s="36">
+      <c r="AB233" s="36">
         <f>AB135*$I$18+AB141*$I$19+AB162*$I$20+AB170*$I$21+AB191*$I$22+AB197*$I$23</f>
         <v/>
       </c>
-      <c r="AC232" s="36">
+      <c r="AC233" s="36">
         <f>AC135*$I$18+AC141*$I$19+AC162*$I$20+AC170*$I$21+AC191*$I$22+AC197*$I$23</f>
         <v/>
       </c>
-      <c r="AD232" s="36">
+      <c r="AD233" s="36">
         <f>AD135*$I$18+AD141*$I$19+AD162*$I$20+AD170*$I$21+AD191*$I$22+AD197*$I$23</f>
         <v/>
       </c>
-      <c r="AE232" s="36">
+      <c r="AE233" s="36">
         <f>AE135*$I$18+AE141*$I$19+AE162*$I$20+AE170*$I$21+AE191*$I$22+AE197*$I$23</f>
         <v/>
       </c>
-      <c r="AF232" s="36">
+      <c r="AF233" s="36">
         <f>AF135*$I$18+AF141*$I$19+AF162*$I$20+AF170*$I$21+AF191*$I$22+AF197*$I$23</f>
         <v/>
       </c>
-      <c r="AG232" s="36">
+      <c r="AG233" s="36">
         <f>AG135*$I$18+AG141*$I$19+AG162*$I$20+AG170*$I$21+AG191*$I$22+AG197*$I$23</f>
         <v/>
       </c>
-      <c r="AH232" s="36">
+      <c r="AH233" s="36">
         <f>AH135*$I$18+AH141*$I$19+AH162*$I$20+AH170*$I$21+AH191*$I$22+AH197*$I$23</f>
         <v/>
       </c>
-      <c r="AI232" s="36">
+      <c r="AI233" s="36">
         <f>AI135*$I$18+AI141*$I$19+AI162*$I$20+AI170*$I$21+AI191*$I$22+AI197*$I$23</f>
         <v/>
       </c>
-      <c r="AJ232" s="36">
+      <c r="AJ233" s="36">
         <f>AJ135*$I$18+AJ141*$I$19+AJ162*$I$20+AJ170*$I$21+AJ191*$I$22+AJ197*$I$23</f>
         <v/>
       </c>
-      <c r="AK232" s="36">
+      <c r="AK233" s="36">
         <f>AK135*$I$18+AK141*$I$19+AK162*$I$20+AK170*$I$21+AK191*$I$22+AK197*$I$23</f>
         <v/>
       </c>
-      <c r="AL232" s="36">
+      <c r="AL233" s="36">
         <f>AL135*$I$18+AL141*$I$19+AL162*$I$20+AL170*$I$21+AL191*$I$22+AL197*$I$23</f>
         <v/>
       </c>
-      <c r="AM232" s="36">
+      <c r="AM233" s="36">
         <f>AM135*$I$18+AM141*$I$19+AM162*$I$20+AM170*$I$21+AM191*$I$22+AM197*$I$23</f>
         <v/>
       </c>
-      <c r="AN232" s="36">
+      <c r="AN233" s="36">
         <f>AN135*$I$18+AN141*$I$19+AN162*$I$20+AN170*$I$21+AN191*$I$22+AN197*$I$23</f>
         <v/>
       </c>
-      <c r="AO232" s="36">
+      <c r="AO233" s="36">
         <f>AO135*$I$18+AO141*$I$19+AO162*$I$20+AO170*$I$21+AO191*$I$22+AO197*$I$23</f>
         <v/>
       </c>
-      <c r="AP232" s="36">
+      <c r="AP233" s="36">
         <f>AP135*$I$18+AP141*$I$19+AP162*$I$20+AP170*$I$21+AP191*$I$22+AP197*$I$23</f>
         <v/>
       </c>
-      <c r="AQ232" s="36">
+      <c r="AQ233" s="36">
         <f>AQ135*$I$18+AQ141*$I$19+AQ162*$I$20+AQ170*$I$21+AQ191*$I$22+AQ197*$I$23</f>
         <v/>
       </c>
-      <c r="AR232" s="36">
+      <c r="AR233" s="36">
         <f>AR135*$I$18+AR141*$I$19+AR162*$I$20+AR170*$I$21+AR191*$I$22+AR197*$I$23</f>
         <v/>
       </c>
-      <c r="AS232" s="36">
+      <c r="AS233" s="36">
         <f>AS135*$I$18+AS141*$I$19+AS162*$I$20+AS170*$I$21+AS191*$I$22+AS197*$I$23</f>
         <v/>
       </c>
-      <c r="AT232" s="36">
+      <c r="AT233" s="36">
         <f>AT135*$I$18+AT141*$I$19+AT162*$I$20+AT170*$I$21+AT191*$I$22+AT197*$I$23</f>
         <v/>
       </c>
-      <c r="AU232" s="36">
+      <c r="AU233" s="36">
         <f>AU135*$I$18+AU141*$I$19+AU162*$I$20+AU170*$I$21+AU191*$I$22+AU197*$I$23</f>
         <v/>
       </c>
-      <c r="AV232" s="36">
+      <c r="AV233" s="36">
         <f>AV135*$I$18+AV141*$I$19+AV162*$I$20+AV170*$I$21+AV191*$I$22+AV197*$I$23</f>
         <v/>
       </c>
-      <c r="AW232" s="36">
+      <c r="AW233" s="36">
         <f>AW135*$I$18+AW141*$I$19+AW162*$I$20+AW170*$I$21+AW191*$I$22+AW197*$I$23</f>
         <v/>
       </c>
-      <c r="AX232" s="36">
+      <c r="AX233" s="36">
         <f>AX135*$I$18+AX141*$I$19+AX162*$I$20+AX170*$I$21+AX191*$I$22+AX197*$I$23</f>
         <v/>
       </c>
-      <c r="AY232" s="36">
+      <c r="AY233" s="36">
         <f>AY135*$I$18+AY141*$I$19+AY162*$I$20+AY170*$I$21+AY191*$I$22+AY197*$I$23</f>
         <v/>
       </c>
-      <c r="AZ232" s="36">
+      <c r="AZ233" s="36">
         <f>AZ135*$I$18+AZ141*$I$19+AZ162*$I$20+AZ170*$I$21+AZ191*$I$22+AZ197*$I$23</f>
         <v/>
       </c>
-      <c r="BA232" s="36">
+      <c r="BA233" s="36">
         <f>BA135*$I$18+BA141*$I$19+BA162*$I$20+BA170*$I$21+BA191*$I$22+BA197*$I$23</f>
         <v/>
       </c>
-      <c r="BB232" s="36">
+      <c r="BB233" s="36">
         <f>BB135*$I$18+BB141*$I$19+BB162*$I$20+BB170*$I$21+BB191*$I$22+BB197*$I$23</f>
         <v/>
       </c>
-      <c r="BC232" s="36">
+      <c r="BC233" s="36">
         <f>BC135*$I$18+BC141*$I$19+BC162*$I$20+BC170*$I$21+BC191*$I$22+BC197*$I$23</f>
         <v/>
       </c>
-      <c r="BD232" s="36">
+      <c r="BD233" s="36">
         <f>BD135*$I$18+BD141*$I$19+BD162*$I$20+BD170*$I$21+BD191*$I$22+BD197*$I$23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  packaging</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E233" s="36">
-        <f>E151+E180+E207</f>
-        <v/>
-      </c>
-      <c r="F233" s="36">
-        <f>F151+F180+F207</f>
-        <v/>
-      </c>
-      <c r="G233" s="36">
-        <f>G151+G180+G207</f>
-        <v/>
-      </c>
-      <c r="H233" s="36">
-        <f>H151+H180+H207</f>
-        <v/>
-      </c>
-      <c r="I233" s="36">
-        <f>I151+I180+I207</f>
-        <v/>
-      </c>
-      <c r="J233" s="36">
-        <f>J151+J180+J207</f>
-        <v/>
-      </c>
-      <c r="K233" s="36">
-        <f>K151+K180+K207</f>
-        <v/>
-      </c>
-      <c r="L233" s="36">
-        <f>L151+L180+L207</f>
-        <v/>
-      </c>
-      <c r="M233" s="36">
-        <f>M151+M180+M207</f>
-        <v/>
-      </c>
-      <c r="N233" s="36">
-        <f>N151+N180+N207</f>
-        <v/>
-      </c>
-      <c r="O233" s="36">
-        <f>O151+O180+O207</f>
-        <v/>
-      </c>
-      <c r="P233" s="36">
-        <f>P151+P180+P207</f>
-        <v/>
-      </c>
-      <c r="Q233" s="36">
-        <f>Q151+Q180+Q207</f>
-        <v/>
-      </c>
-      <c r="R233" s="36">
-        <f>R151+R180+R207</f>
-        <v/>
-      </c>
-      <c r="S233" s="36">
-        <f>S151+S180+S207</f>
-        <v/>
-      </c>
-      <c r="T233" s="36">
-        <f>T151+T180+T207</f>
-        <v/>
-      </c>
-      <c r="U233" s="36">
-        <f>U151+U180+U207</f>
-        <v/>
-      </c>
-      <c r="V233" s="36">
-        <f>V151+V180+V207</f>
-        <v/>
-      </c>
-      <c r="W233" s="36">
-        <f>W151+W180+W207</f>
-        <v/>
-      </c>
-      <c r="X233" s="36">
-        <f>X151+X180+X207</f>
-        <v/>
-      </c>
-      <c r="Y233" s="36">
-        <f>Y151+Y180+Y207</f>
-        <v/>
-      </c>
-      <c r="Z233" s="36">
-        <f>Z151+Z180+Z207</f>
-        <v/>
-      </c>
-      <c r="AA233" s="36">
-        <f>AA151+AA180+AA207</f>
-        <v/>
-      </c>
-      <c r="AB233" s="36">
-        <f>AB151+AB180+AB207</f>
-        <v/>
-      </c>
-      <c r="AC233" s="36">
-        <f>AC151+AC180+AC207</f>
-        <v/>
-      </c>
-      <c r="AD233" s="36">
-        <f>AD151+AD180+AD207</f>
-        <v/>
-      </c>
-      <c r="AE233" s="36">
-        <f>AE151+AE180+AE207</f>
-        <v/>
-      </c>
-      <c r="AF233" s="36">
-        <f>AF151+AF180+AF207</f>
-        <v/>
-      </c>
-      <c r="AG233" s="36">
-        <f>AG151+AG180+AG207</f>
-        <v/>
-      </c>
-      <c r="AH233" s="36">
-        <f>AH151+AH180+AH207</f>
-        <v/>
-      </c>
-      <c r="AI233" s="36">
-        <f>AI151+AI180+AI207</f>
-        <v/>
-      </c>
-      <c r="AJ233" s="36">
-        <f>AJ151+AJ180+AJ207</f>
-        <v/>
-      </c>
-      <c r="AK233" s="36">
-        <f>AK151+AK180+AK207</f>
-        <v/>
-      </c>
-      <c r="AL233" s="36">
-        <f>AL151+AL180+AL207</f>
-        <v/>
-      </c>
-      <c r="AM233" s="36">
-        <f>AM151+AM180+AM207</f>
-        <v/>
-      </c>
-      <c r="AN233" s="36">
-        <f>AN151+AN180+AN207</f>
-        <v/>
-      </c>
-      <c r="AO233" s="36">
-        <f>AO151+AO180+AO207</f>
-        <v/>
-      </c>
-      <c r="AP233" s="36">
-        <f>AP151+AP180+AP207</f>
-        <v/>
-      </c>
-      <c r="AQ233" s="36">
-        <f>AQ151+AQ180+AQ207</f>
-        <v/>
-      </c>
-      <c r="AR233" s="36">
-        <f>AR151+AR180+AR207</f>
-        <v/>
-      </c>
-      <c r="AS233" s="36">
-        <f>AS151+AS180+AS207</f>
-        <v/>
-      </c>
-      <c r="AT233" s="36">
-        <f>AT151+AT180+AT207</f>
-        <v/>
-      </c>
-      <c r="AU233" s="36">
-        <f>AU151+AU180+AU207</f>
-        <v/>
-      </c>
-      <c r="AV233" s="36">
-        <f>AV151+AV180+AV207</f>
-        <v/>
-      </c>
-      <c r="AW233" s="36">
-        <f>AW151+AW180+AW207</f>
-        <v/>
-      </c>
-      <c r="AX233" s="36">
-        <f>AX151+AX180+AX207</f>
-        <v/>
-      </c>
-      <c r="AY233" s="36">
-        <f>AY151+AY180+AY207</f>
-        <v/>
-      </c>
-      <c r="AZ233" s="36">
-        <f>AZ151+AZ180+AZ207</f>
-        <v/>
-      </c>
-      <c r="BA233" s="36">
-        <f>BA151+BA180+BA207</f>
-        <v/>
-      </c>
-      <c r="BB233" s="36">
-        <f>BB151+BB180+BB207</f>
-        <v/>
-      </c>
-      <c r="BC233" s="36">
-        <f>BC151+BC180+BC207</f>
-        <v/>
-      </c>
-      <c r="BD233" s="36">
-        <f>BD151+BD180+BD207</f>
         <v/>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  growing cost</t>
+          <t xml:space="preserve">  packaging</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -28783,218 +28748,218 @@
         </is>
       </c>
       <c r="E234" s="36">
-        <f>E150+E179+E206</f>
+        <f>E151+E180+E207</f>
         <v/>
       </c>
       <c r="F234" s="36">
-        <f>F150+F179+F206</f>
+        <f>F151+F180+F207</f>
         <v/>
       </c>
       <c r="G234" s="36">
-        <f>G150+G179+G206</f>
+        <f>G151+G180+G207</f>
         <v/>
       </c>
       <c r="H234" s="36">
-        <f>H150+H179+H206</f>
+        <f>H151+H180+H207</f>
         <v/>
       </c>
       <c r="I234" s="36">
-        <f>I150+I179+I206</f>
+        <f>I151+I180+I207</f>
         <v/>
       </c>
       <c r="J234" s="36">
-        <f>J150+J179+J206</f>
+        <f>J151+J180+J207</f>
         <v/>
       </c>
       <c r="K234" s="36">
-        <f>K150+K179+K206</f>
+        <f>K151+K180+K207</f>
         <v/>
       </c>
       <c r="L234" s="36">
-        <f>L150+L179+L206</f>
+        <f>L151+L180+L207</f>
         <v/>
       </c>
       <c r="M234" s="36">
-        <f>M150+M179+M206</f>
+        <f>M151+M180+M207</f>
         <v/>
       </c>
       <c r="N234" s="36">
-        <f>N150+N179+N206</f>
+        <f>N151+N180+N207</f>
         <v/>
       </c>
       <c r="O234" s="36">
-        <f>O150+O179+O206</f>
+        <f>O151+O180+O207</f>
         <v/>
       </c>
       <c r="P234" s="36">
-        <f>P150+P179+P206</f>
+        <f>P151+P180+P207</f>
         <v/>
       </c>
       <c r="Q234" s="36">
-        <f>Q150+Q179+Q206</f>
+        <f>Q151+Q180+Q207</f>
         <v/>
       </c>
       <c r="R234" s="36">
-        <f>R150+R179+R206</f>
+        <f>R151+R180+R207</f>
         <v/>
       </c>
       <c r="S234" s="36">
-        <f>S150+S179+S206</f>
+        <f>S151+S180+S207</f>
         <v/>
       </c>
       <c r="T234" s="36">
-        <f>T150+T179+T206</f>
+        <f>T151+T180+T207</f>
         <v/>
       </c>
       <c r="U234" s="36">
-        <f>U150+U179+U206</f>
+        <f>U151+U180+U207</f>
         <v/>
       </c>
       <c r="V234" s="36">
-        <f>V150+V179+V206</f>
+        <f>V151+V180+V207</f>
         <v/>
       </c>
       <c r="W234" s="36">
-        <f>W150+W179+W206</f>
+        <f>W151+W180+W207</f>
         <v/>
       </c>
       <c r="X234" s="36">
-        <f>X150+X179+X206</f>
+        <f>X151+X180+X207</f>
         <v/>
       </c>
       <c r="Y234" s="36">
-        <f>Y150+Y179+Y206</f>
+        <f>Y151+Y180+Y207</f>
         <v/>
       </c>
       <c r="Z234" s="36">
-        <f>Z150+Z179+Z206</f>
+        <f>Z151+Z180+Z207</f>
         <v/>
       </c>
       <c r="AA234" s="36">
-        <f>AA150+AA179+AA206</f>
+        <f>AA151+AA180+AA207</f>
         <v/>
       </c>
       <c r="AB234" s="36">
-        <f>AB150+AB179+AB206</f>
+        <f>AB151+AB180+AB207</f>
         <v/>
       </c>
       <c r="AC234" s="36">
-        <f>AC150+AC179+AC206</f>
+        <f>AC151+AC180+AC207</f>
         <v/>
       </c>
       <c r="AD234" s="36">
-        <f>AD150+AD179+AD206</f>
+        <f>AD151+AD180+AD207</f>
         <v/>
       </c>
       <c r="AE234" s="36">
-        <f>AE150+AE179+AE206</f>
+        <f>AE151+AE180+AE207</f>
         <v/>
       </c>
       <c r="AF234" s="36">
-        <f>AF150+AF179+AF206</f>
+        <f>AF151+AF180+AF207</f>
         <v/>
       </c>
       <c r="AG234" s="36">
-        <f>AG150+AG179+AG206</f>
+        <f>AG151+AG180+AG207</f>
         <v/>
       </c>
       <c r="AH234" s="36">
-        <f>AH150+AH179+AH206</f>
+        <f>AH151+AH180+AH207</f>
         <v/>
       </c>
       <c r="AI234" s="36">
-        <f>AI150+AI179+AI206</f>
+        <f>AI151+AI180+AI207</f>
         <v/>
       </c>
       <c r="AJ234" s="36">
-        <f>AJ150+AJ179+AJ206</f>
+        <f>AJ151+AJ180+AJ207</f>
         <v/>
       </c>
       <c r="AK234" s="36">
-        <f>AK150+AK179+AK206</f>
+        <f>AK151+AK180+AK207</f>
         <v/>
       </c>
       <c r="AL234" s="36">
-        <f>AL150+AL179+AL206</f>
+        <f>AL151+AL180+AL207</f>
         <v/>
       </c>
       <c r="AM234" s="36">
-        <f>AM150+AM179+AM206</f>
+        <f>AM151+AM180+AM207</f>
         <v/>
       </c>
       <c r="AN234" s="36">
-        <f>AN150+AN179+AN206</f>
+        <f>AN151+AN180+AN207</f>
         <v/>
       </c>
       <c r="AO234" s="36">
-        <f>AO150+AO179+AO206</f>
+        <f>AO151+AO180+AO207</f>
         <v/>
       </c>
       <c r="AP234" s="36">
-        <f>AP150+AP179+AP206</f>
+        <f>AP151+AP180+AP207</f>
         <v/>
       </c>
       <c r="AQ234" s="36">
-        <f>AQ150+AQ179+AQ206</f>
+        <f>AQ151+AQ180+AQ207</f>
         <v/>
       </c>
       <c r="AR234" s="36">
-        <f>AR150+AR179+AR206</f>
+        <f>AR151+AR180+AR207</f>
         <v/>
       </c>
       <c r="AS234" s="36">
-        <f>AS150+AS179+AS206</f>
+        <f>AS151+AS180+AS207</f>
         <v/>
       </c>
       <c r="AT234" s="36">
-        <f>AT150+AT179+AT206</f>
+        <f>AT151+AT180+AT207</f>
         <v/>
       </c>
       <c r="AU234" s="36">
-        <f>AU150+AU179+AU206</f>
+        <f>AU151+AU180+AU207</f>
         <v/>
       </c>
       <c r="AV234" s="36">
-        <f>AV150+AV179+AV206</f>
+        <f>AV151+AV180+AV207</f>
         <v/>
       </c>
       <c r="AW234" s="36">
-        <f>AW150+AW179+AW206</f>
+        <f>AW151+AW180+AW207</f>
         <v/>
       </c>
       <c r="AX234" s="36">
-        <f>AX150+AX179+AX206</f>
+        <f>AX151+AX180+AX207</f>
         <v/>
       </c>
       <c r="AY234" s="36">
-        <f>AY150+AY179+AY206</f>
+        <f>AY151+AY180+AY207</f>
         <v/>
       </c>
       <c r="AZ234" s="36">
-        <f>AZ150+AZ179+AZ206</f>
+        <f>AZ151+AZ180+AZ207</f>
         <v/>
       </c>
       <c r="BA234" s="36">
-        <f>BA150+BA179+BA206</f>
+        <f>BA151+BA180+BA207</f>
         <v/>
       </c>
       <c r="BB234" s="36">
-        <f>BB150+BB179+BB206</f>
+        <f>BB151+BB180+BB207</f>
         <v/>
       </c>
       <c r="BC234" s="36">
-        <f>BC150+BC179+BC206</f>
+        <f>BC151+BC180+BC207</f>
         <v/>
       </c>
       <c r="BD234" s="36">
-        <f>BD150+BD179+BD206</f>
+        <f>BD151+BD180+BD207</f>
         <v/>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fixed cost</t>
+          <t xml:space="preserve">  growing cost</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -29003,218 +28968,218 @@
         </is>
       </c>
       <c r="E235" s="36">
-        <f>$B$228</f>
+        <f>E150+E179+E206</f>
         <v/>
       </c>
       <c r="F235" s="36">
-        <f>$B$228</f>
+        <f>F150+F179+F206</f>
         <v/>
       </c>
       <c r="G235" s="36">
-        <f>$B$228</f>
+        <f>G150+G179+G206</f>
         <v/>
       </c>
       <c r="H235" s="36">
-        <f>$B$228</f>
+        <f>H150+H179+H206</f>
         <v/>
       </c>
       <c r="I235" s="36">
-        <f>$B$228</f>
+        <f>I150+I179+I206</f>
         <v/>
       </c>
       <c r="J235" s="36">
-        <f>$B$228</f>
+        <f>J150+J179+J206</f>
         <v/>
       </c>
       <c r="K235" s="36">
-        <f>$B$228</f>
+        <f>K150+K179+K206</f>
         <v/>
       </c>
       <c r="L235" s="36">
-        <f>$B$228</f>
+        <f>L150+L179+L206</f>
         <v/>
       </c>
       <c r="M235" s="36">
-        <f>$B$228</f>
+        <f>M150+M179+M206</f>
         <v/>
       </c>
       <c r="N235" s="36">
-        <f>$B$228</f>
+        <f>N150+N179+N206</f>
         <v/>
       </c>
       <c r="O235" s="36">
-        <f>$B$228</f>
+        <f>O150+O179+O206</f>
         <v/>
       </c>
       <c r="P235" s="36">
-        <f>$B$228</f>
+        <f>P150+P179+P206</f>
         <v/>
       </c>
       <c r="Q235" s="36">
-        <f>$B$228</f>
+        <f>Q150+Q179+Q206</f>
         <v/>
       </c>
       <c r="R235" s="36">
-        <f>$B$228</f>
+        <f>R150+R179+R206</f>
         <v/>
       </c>
       <c r="S235" s="36">
-        <f>$B$228</f>
+        <f>S150+S179+S206</f>
         <v/>
       </c>
       <c r="T235" s="36">
-        <f>$B$228</f>
+        <f>T150+T179+T206</f>
         <v/>
       </c>
       <c r="U235" s="36">
-        <f>$B$228</f>
+        <f>U150+U179+U206</f>
         <v/>
       </c>
       <c r="V235" s="36">
-        <f>$B$228</f>
+        <f>V150+V179+V206</f>
         <v/>
       </c>
       <c r="W235" s="36">
-        <f>$B$228</f>
+        <f>W150+W179+W206</f>
         <v/>
       </c>
       <c r="X235" s="36">
-        <f>$B$228</f>
+        <f>X150+X179+X206</f>
         <v/>
       </c>
       <c r="Y235" s="36">
-        <f>$B$228</f>
+        <f>Y150+Y179+Y206</f>
         <v/>
       </c>
       <c r="Z235" s="36">
-        <f>$B$228</f>
+        <f>Z150+Z179+Z206</f>
         <v/>
       </c>
       <c r="AA235" s="36">
-        <f>$B$228</f>
+        <f>AA150+AA179+AA206</f>
         <v/>
       </c>
       <c r="AB235" s="36">
-        <f>$B$228</f>
+        <f>AB150+AB179+AB206</f>
         <v/>
       </c>
       <c r="AC235" s="36">
-        <f>$B$228</f>
+        <f>AC150+AC179+AC206</f>
         <v/>
       </c>
       <c r="AD235" s="36">
-        <f>$B$228</f>
+        <f>AD150+AD179+AD206</f>
         <v/>
       </c>
       <c r="AE235" s="36">
-        <f>$B$228</f>
+        <f>AE150+AE179+AE206</f>
         <v/>
       </c>
       <c r="AF235" s="36">
-        <f>$B$228</f>
+        <f>AF150+AF179+AF206</f>
         <v/>
       </c>
       <c r="AG235" s="36">
-        <f>$B$228</f>
+        <f>AG150+AG179+AG206</f>
         <v/>
       </c>
       <c r="AH235" s="36">
-        <f>$B$228</f>
+        <f>AH150+AH179+AH206</f>
         <v/>
       </c>
       <c r="AI235" s="36">
-        <f>$B$228</f>
+        <f>AI150+AI179+AI206</f>
         <v/>
       </c>
       <c r="AJ235" s="36">
-        <f>$B$228</f>
+        <f>AJ150+AJ179+AJ206</f>
         <v/>
       </c>
       <c r="AK235" s="36">
-        <f>$B$228</f>
+        <f>AK150+AK179+AK206</f>
         <v/>
       </c>
       <c r="AL235" s="36">
-        <f>$B$228</f>
+        <f>AL150+AL179+AL206</f>
         <v/>
       </c>
       <c r="AM235" s="36">
-        <f>$B$228</f>
+        <f>AM150+AM179+AM206</f>
         <v/>
       </c>
       <c r="AN235" s="36">
-        <f>$B$228</f>
+        <f>AN150+AN179+AN206</f>
         <v/>
       </c>
       <c r="AO235" s="36">
-        <f>$B$228</f>
+        <f>AO150+AO179+AO206</f>
         <v/>
       </c>
       <c r="AP235" s="36">
-        <f>$B$228</f>
+        <f>AP150+AP179+AP206</f>
         <v/>
       </c>
       <c r="AQ235" s="36">
-        <f>$B$228</f>
+        <f>AQ150+AQ179+AQ206</f>
         <v/>
       </c>
       <c r="AR235" s="36">
-        <f>$B$228</f>
+        <f>AR150+AR179+AR206</f>
         <v/>
       </c>
       <c r="AS235" s="36">
-        <f>$B$228</f>
+        <f>AS150+AS179+AS206</f>
         <v/>
       </c>
       <c r="AT235" s="36">
-        <f>$B$228</f>
+        <f>AT150+AT179+AT206</f>
         <v/>
       </c>
       <c r="AU235" s="36">
-        <f>$B$228</f>
+        <f>AU150+AU179+AU206</f>
         <v/>
       </c>
       <c r="AV235" s="36">
-        <f>$B$228</f>
+        <f>AV150+AV179+AV206</f>
         <v/>
       </c>
       <c r="AW235" s="36">
-        <f>$B$228</f>
+        <f>AW150+AW179+AW206</f>
         <v/>
       </c>
       <c r="AX235" s="36">
-        <f>$B$228</f>
+        <f>AX150+AX179+AX206</f>
         <v/>
       </c>
       <c r="AY235" s="36">
-        <f>$B$228</f>
+        <f>AY150+AY179+AY206</f>
         <v/>
       </c>
       <c r="AZ235" s="36">
-        <f>$B$228</f>
+        <f>AZ150+AZ179+AZ206</f>
         <v/>
       </c>
       <c r="BA235" s="36">
-        <f>$B$228</f>
+        <f>BA150+BA179+BA206</f>
         <v/>
       </c>
       <c r="BB235" s="36">
-        <f>$B$228</f>
+        <f>BB150+BB179+BB206</f>
         <v/>
       </c>
       <c r="BC235" s="36">
-        <f>$B$228</f>
+        <f>BC150+BC179+BC206</f>
         <v/>
       </c>
       <c r="BD235" s="36">
-        <f>$B$228</f>
+        <f>BD150+BD179+BD206</f>
         <v/>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  overhead</t>
+          <t xml:space="preserve">  fixed cost</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -29223,2259 +29188,2525 @@
         </is>
       </c>
       <c r="E236" s="36">
-        <f>E232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="F236" s="36">
-        <f>F232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="G236" s="36">
-        <f>G232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="H236" s="36">
-        <f>H232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="I236" s="36">
-        <f>I232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="J236" s="36">
-        <f>J232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="K236" s="36">
-        <f>K232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="L236" s="36">
-        <f>L232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="M236" s="36">
-        <f>M232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="N236" s="36">
-        <f>N232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="O236" s="36">
-        <f>O232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="P236" s="36">
-        <f>P232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="Q236" s="36">
-        <f>Q232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="R236" s="36">
-        <f>R232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="S236" s="36">
-        <f>S232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="T236" s="36">
-        <f>T232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="U236" s="36">
-        <f>U232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="V236" s="36">
-        <f>V232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="W236" s="36">
-        <f>W232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="X236" s="36">
-        <f>X232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="Y236" s="36">
-        <f>Y232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="Z236" s="36">
-        <f>Z232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AA236" s="36">
-        <f>AA232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AB236" s="36">
-        <f>AB232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AC236" s="36">
-        <f>AC232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AD236" s="36">
-        <f>AD232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AE236" s="36">
-        <f>AE232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AF236" s="36">
-        <f>AF232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AG236" s="36">
-        <f>AG232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AH236" s="36">
-        <f>AH232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AI236" s="36">
-        <f>AI232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AJ236" s="36">
-        <f>AJ232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AK236" s="36">
-        <f>AK232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AL236" s="36">
-        <f>AL232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AM236" s="36">
-        <f>AM232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AN236" s="36">
-        <f>AN232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AO236" s="36">
-        <f>AO232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AP236" s="36">
-        <f>AP232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AQ236" s="36">
-        <f>AQ232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AR236" s="36">
-        <f>AR232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AS236" s="36">
-        <f>AS232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AT236" s="36">
-        <f>AT232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AU236" s="36">
-        <f>AU232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AV236" s="36">
-        <f>AV232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AW236" s="36">
-        <f>AW232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AX236" s="36">
-        <f>AX232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AY236" s="36">
-        <f>AY232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="AZ236" s="36">
-        <f>AZ232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="BA236" s="36">
-        <f>BA232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="BB236" s="36">
-        <f>BB232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="BC236" s="36">
-        <f>BC232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
       <c r="BD236" s="36">
-        <f>BD232*$B$229</f>
+        <f>$B$228</f>
         <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="27" t="inlineStr">
         <is>
+          <t xml:space="preserve">  overhead</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E237" s="36">
+        <f>E233*$B$229</f>
+        <v/>
+      </c>
+      <c r="F237" s="36">
+        <f>F233*$B$229</f>
+        <v/>
+      </c>
+      <c r="G237" s="36">
+        <f>G233*$B$229</f>
+        <v/>
+      </c>
+      <c r="H237" s="36">
+        <f>H233*$B$229</f>
+        <v/>
+      </c>
+      <c r="I237" s="36">
+        <f>I233*$B$229</f>
+        <v/>
+      </c>
+      <c r="J237" s="36">
+        <f>J233*$B$229</f>
+        <v/>
+      </c>
+      <c r="K237" s="36">
+        <f>K233*$B$229</f>
+        <v/>
+      </c>
+      <c r="L237" s="36">
+        <f>L233*$B$229</f>
+        <v/>
+      </c>
+      <c r="M237" s="36">
+        <f>M233*$B$229</f>
+        <v/>
+      </c>
+      <c r="N237" s="36">
+        <f>N233*$B$229</f>
+        <v/>
+      </c>
+      <c r="O237" s="36">
+        <f>O233*$B$229</f>
+        <v/>
+      </c>
+      <c r="P237" s="36">
+        <f>P233*$B$229</f>
+        <v/>
+      </c>
+      <c r="Q237" s="36">
+        <f>Q233*$B$229</f>
+        <v/>
+      </c>
+      <c r="R237" s="36">
+        <f>R233*$B$229</f>
+        <v/>
+      </c>
+      <c r="S237" s="36">
+        <f>S233*$B$229</f>
+        <v/>
+      </c>
+      <c r="T237" s="36">
+        <f>T233*$B$229</f>
+        <v/>
+      </c>
+      <c r="U237" s="36">
+        <f>U233*$B$229</f>
+        <v/>
+      </c>
+      <c r="V237" s="36">
+        <f>V233*$B$229</f>
+        <v/>
+      </c>
+      <c r="W237" s="36">
+        <f>W233*$B$229</f>
+        <v/>
+      </c>
+      <c r="X237" s="36">
+        <f>X233*$B$229</f>
+        <v/>
+      </c>
+      <c r="Y237" s="36">
+        <f>Y233*$B$229</f>
+        <v/>
+      </c>
+      <c r="Z237" s="36">
+        <f>Z233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AA237" s="36">
+        <f>AA233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AB237" s="36">
+        <f>AB233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AC237" s="36">
+        <f>AC233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AD237" s="36">
+        <f>AD233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AE237" s="36">
+        <f>AE233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AF237" s="36">
+        <f>AF233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AG237" s="36">
+        <f>AG233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AH237" s="36">
+        <f>AH233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AI237" s="36">
+        <f>AI233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AJ237" s="36">
+        <f>AJ233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AK237" s="36">
+        <f>AK233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AL237" s="36">
+        <f>AL233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AM237" s="36">
+        <f>AM233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AN237" s="36">
+        <f>AN233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AO237" s="36">
+        <f>AO233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AP237" s="36">
+        <f>AP233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AQ237" s="36">
+        <f>AQ233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AR237" s="36">
+        <f>AR233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AS237" s="36">
+        <f>AS233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AT237" s="36">
+        <f>AT233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AU237" s="36">
+        <f>AU233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AV237" s="36">
+        <f>AV233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AW237" s="36">
+        <f>AW233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AX237" s="36">
+        <f>AX233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AY237" s="36">
+        <f>AY233*$B$229</f>
+        <v/>
+      </c>
+      <c r="AZ237" s="36">
+        <f>AZ233*$B$229</f>
+        <v/>
+      </c>
+      <c r="BA237" s="36">
+        <f>BA233*$B$229</f>
+        <v/>
+      </c>
+      <c r="BB237" s="36">
+        <f>BB233*$B$229</f>
+        <v/>
+      </c>
+      <c r="BC237" s="36">
+        <f>BC233*$B$229</f>
+        <v/>
+      </c>
+      <c r="BD237" s="36">
+        <f>BD233*$B$229</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="27" t="inlineStr">
+        <is>
           <t xml:space="preserve">  wages</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E237" s="36">
+      <c r="E238" s="36">
         <f>E117</f>
         <v/>
       </c>
-      <c r="F237" s="36">
+      <c r="F238" s="36">
         <f>F117</f>
         <v/>
       </c>
-      <c r="G237" s="36">
+      <c r="G238" s="36">
         <f>G117</f>
         <v/>
       </c>
-      <c r="H237" s="36">
+      <c r="H238" s="36">
         <f>H117</f>
         <v/>
       </c>
-      <c r="I237" s="36">
+      <c r="I238" s="36">
         <f>I117</f>
         <v/>
       </c>
-      <c r="J237" s="36">
+      <c r="J238" s="36">
         <f>J117</f>
         <v/>
       </c>
-      <c r="K237" s="36">
+      <c r="K238" s="36">
         <f>K117</f>
         <v/>
       </c>
-      <c r="L237" s="36">
+      <c r="L238" s="36">
         <f>L117</f>
         <v/>
       </c>
-      <c r="M237" s="36">
+      <c r="M238" s="36">
         <f>M117</f>
         <v/>
       </c>
-      <c r="N237" s="36">
+      <c r="N238" s="36">
         <f>N117</f>
         <v/>
       </c>
-      <c r="O237" s="36">
+      <c r="O238" s="36">
         <f>O117</f>
         <v/>
       </c>
-      <c r="P237" s="36">
+      <c r="P238" s="36">
         <f>P117</f>
         <v/>
       </c>
-      <c r="Q237" s="36">
+      <c r="Q238" s="36">
         <f>Q117</f>
         <v/>
       </c>
-      <c r="R237" s="36">
+      <c r="R238" s="36">
         <f>R117</f>
         <v/>
       </c>
-      <c r="S237" s="36">
+      <c r="S238" s="36">
         <f>S117</f>
         <v/>
       </c>
-      <c r="T237" s="36">
+      <c r="T238" s="36">
         <f>T117</f>
         <v/>
       </c>
-      <c r="U237" s="36">
+      <c r="U238" s="36">
         <f>U117</f>
         <v/>
       </c>
-      <c r="V237" s="36">
+      <c r="V238" s="36">
         <f>V117</f>
         <v/>
       </c>
-      <c r="W237" s="36">
+      <c r="W238" s="36">
         <f>W117</f>
         <v/>
       </c>
-      <c r="X237" s="36">
+      <c r="X238" s="36">
         <f>X117</f>
         <v/>
       </c>
-      <c r="Y237" s="36">
+      <c r="Y238" s="36">
         <f>Y117</f>
         <v/>
       </c>
-      <c r="Z237" s="36">
+      <c r="Z238" s="36">
         <f>Z117</f>
         <v/>
       </c>
-      <c r="AA237" s="36">
+      <c r="AA238" s="36">
         <f>AA117</f>
         <v/>
       </c>
-      <c r="AB237" s="36">
+      <c r="AB238" s="36">
         <f>AB117</f>
         <v/>
       </c>
-      <c r="AC237" s="36">
+      <c r="AC238" s="36">
         <f>AC117</f>
         <v/>
       </c>
-      <c r="AD237" s="36">
+      <c r="AD238" s="36">
         <f>AD117</f>
         <v/>
       </c>
-      <c r="AE237" s="36">
+      <c r="AE238" s="36">
         <f>AE117</f>
         <v/>
       </c>
-      <c r="AF237" s="36">
+      <c r="AF238" s="36">
         <f>AF117</f>
         <v/>
       </c>
-      <c r="AG237" s="36">
+      <c r="AG238" s="36">
         <f>AG117</f>
         <v/>
       </c>
-      <c r="AH237" s="36">
+      <c r="AH238" s="36">
         <f>AH117</f>
         <v/>
       </c>
-      <c r="AI237" s="36">
+      <c r="AI238" s="36">
         <f>AI117</f>
         <v/>
       </c>
-      <c r="AJ237" s="36">
+      <c r="AJ238" s="36">
         <f>AJ117</f>
         <v/>
       </c>
-      <c r="AK237" s="36">
+      <c r="AK238" s="36">
         <f>AK117</f>
         <v/>
       </c>
-      <c r="AL237" s="36">
+      <c r="AL238" s="36">
         <f>AL117</f>
         <v/>
       </c>
-      <c r="AM237" s="36">
+      <c r="AM238" s="36">
         <f>AM117</f>
         <v/>
       </c>
-      <c r="AN237" s="36">
+      <c r="AN238" s="36">
         <f>AN117</f>
         <v/>
       </c>
-      <c r="AO237" s="36">
+      <c r="AO238" s="36">
         <f>AO117</f>
         <v/>
       </c>
-      <c r="AP237" s="36">
+      <c r="AP238" s="36">
         <f>AP117</f>
         <v/>
       </c>
-      <c r="AQ237" s="36">
+      <c r="AQ238" s="36">
         <f>AQ117</f>
         <v/>
       </c>
-      <c r="AR237" s="36">
+      <c r="AR238" s="36">
         <f>AR117</f>
         <v/>
       </c>
-      <c r="AS237" s="36">
+      <c r="AS238" s="36">
         <f>AS117</f>
         <v/>
       </c>
-      <c r="AT237" s="36">
+      <c r="AT238" s="36">
         <f>AT117</f>
         <v/>
       </c>
-      <c r="AU237" s="36">
+      <c r="AU238" s="36">
         <f>AU117</f>
         <v/>
       </c>
-      <c r="AV237" s="36">
+      <c r="AV238" s="36">
         <f>AV117</f>
         <v/>
       </c>
-      <c r="AW237" s="36">
+      <c r="AW238" s="36">
         <f>AW117</f>
         <v/>
       </c>
-      <c r="AX237" s="36">
+      <c r="AX238" s="36">
         <f>AX117</f>
         <v/>
       </c>
-      <c r="AY237" s="36">
+      <c r="AY238" s="36">
         <f>AY117</f>
         <v/>
       </c>
-      <c r="AZ237" s="36">
+      <c r="AZ238" s="36">
         <f>AZ117</f>
         <v/>
       </c>
-      <c r="BA237" s="36">
+      <c r="BA238" s="36">
         <f>BA117</f>
         <v/>
       </c>
-      <c r="BB237" s="36">
+      <c r="BB238" s="36">
         <f>BB117</f>
         <v/>
       </c>
-      <c r="BC237" s="36">
+      <c r="BC238" s="36">
         <f>BC117</f>
         <v/>
       </c>
-      <c r="BD237" s="36">
+      <c r="BD238" s="36">
         <f>BD117</f>
         <v/>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>NET CASH this week</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E238" s="36">
-        <f>E232-E233-E234-E235-E236-E237</f>
-        <v/>
-      </c>
-      <c r="F238" s="36">
-        <f>F232-F233-F234-F235-F236-F237</f>
-        <v/>
-      </c>
-      <c r="G238" s="36">
-        <f>G232-G233-G234-G235-G236-G237</f>
-        <v/>
-      </c>
-      <c r="H238" s="36">
-        <f>H232-H233-H234-H235-H236-H237</f>
-        <v/>
-      </c>
-      <c r="I238" s="36">
-        <f>I232-I233-I234-I235-I236-I237</f>
-        <v/>
-      </c>
-      <c r="J238" s="36">
-        <f>J232-J233-J234-J235-J236-J237</f>
-        <v/>
-      </c>
-      <c r="K238" s="36">
-        <f>K232-K233-K234-K235-K236-K237</f>
-        <v/>
-      </c>
-      <c r="L238" s="36">
-        <f>L232-L233-L234-L235-L236-L237</f>
-        <v/>
-      </c>
-      <c r="M238" s="36">
-        <f>M232-M233-M234-M235-M236-M237</f>
-        <v/>
-      </c>
-      <c r="N238" s="36">
-        <f>N232-N233-N234-N235-N236-N237</f>
-        <v/>
-      </c>
-      <c r="O238" s="36">
-        <f>O232-O233-O234-O235-O236-O237</f>
-        <v/>
-      </c>
-      <c r="P238" s="36">
-        <f>P232-P233-P234-P235-P236-P237</f>
-        <v/>
-      </c>
-      <c r="Q238" s="36">
-        <f>Q232-Q233-Q234-Q235-Q236-Q237</f>
-        <v/>
-      </c>
-      <c r="R238" s="36">
-        <f>R232-R233-R234-R235-R236-R237</f>
-        <v/>
-      </c>
-      <c r="S238" s="36">
-        <f>S232-S233-S234-S235-S236-S237</f>
-        <v/>
-      </c>
-      <c r="T238" s="36">
-        <f>T232-T233-T234-T235-T236-T237</f>
-        <v/>
-      </c>
-      <c r="U238" s="36">
-        <f>U232-U233-U234-U235-U236-U237</f>
-        <v/>
-      </c>
-      <c r="V238" s="36">
-        <f>V232-V233-V234-V235-V236-V237</f>
-        <v/>
-      </c>
-      <c r="W238" s="36">
-        <f>W232-W233-W234-W235-W236-W237</f>
-        <v/>
-      </c>
-      <c r="X238" s="36">
-        <f>X232-X233-X234-X235-X236-X237</f>
-        <v/>
-      </c>
-      <c r="Y238" s="36">
-        <f>Y232-Y233-Y234-Y235-Y236-Y237</f>
-        <v/>
-      </c>
-      <c r="Z238" s="36">
-        <f>Z232-Z233-Z234-Z235-Z236-Z237</f>
-        <v/>
-      </c>
-      <c r="AA238" s="36">
-        <f>AA232-AA233-AA234-AA235-AA236-AA237</f>
-        <v/>
-      </c>
-      <c r="AB238" s="36">
-        <f>AB232-AB233-AB234-AB235-AB236-AB237</f>
-        <v/>
-      </c>
-      <c r="AC238" s="36">
-        <f>AC232-AC233-AC234-AC235-AC236-AC237</f>
-        <v/>
-      </c>
-      <c r="AD238" s="36">
-        <f>AD232-AD233-AD234-AD235-AD236-AD237</f>
-        <v/>
-      </c>
-      <c r="AE238" s="36">
-        <f>AE232-AE233-AE234-AE235-AE236-AE237</f>
-        <v/>
-      </c>
-      <c r="AF238" s="36">
-        <f>AF232-AF233-AF234-AF235-AF236-AF237</f>
-        <v/>
-      </c>
-      <c r="AG238" s="36">
-        <f>AG232-AG233-AG234-AG235-AG236-AG237</f>
-        <v/>
-      </c>
-      <c r="AH238" s="36">
-        <f>AH232-AH233-AH234-AH235-AH236-AH237</f>
-        <v/>
-      </c>
-      <c r="AI238" s="36">
-        <f>AI232-AI233-AI234-AI235-AI236-AI237</f>
-        <v/>
-      </c>
-      <c r="AJ238" s="36">
-        <f>AJ232-AJ233-AJ234-AJ235-AJ236-AJ237</f>
-        <v/>
-      </c>
-      <c r="AK238" s="36">
-        <f>AK232-AK233-AK234-AK235-AK236-AK237</f>
-        <v/>
-      </c>
-      <c r="AL238" s="36">
-        <f>AL232-AL233-AL234-AL235-AL236-AL237</f>
-        <v/>
-      </c>
-      <c r="AM238" s="36">
-        <f>AM232-AM233-AM234-AM235-AM236-AM237</f>
-        <v/>
-      </c>
-      <c r="AN238" s="36">
-        <f>AN232-AN233-AN234-AN235-AN236-AN237</f>
-        <v/>
-      </c>
-      <c r="AO238" s="36">
-        <f>AO232-AO233-AO234-AO235-AO236-AO237</f>
-        <v/>
-      </c>
-      <c r="AP238" s="36">
-        <f>AP232-AP233-AP234-AP235-AP236-AP237</f>
-        <v/>
-      </c>
-      <c r="AQ238" s="36">
-        <f>AQ232-AQ233-AQ234-AQ235-AQ236-AQ237</f>
-        <v/>
-      </c>
-      <c r="AR238" s="36">
-        <f>AR232-AR233-AR234-AR235-AR236-AR237</f>
-        <v/>
-      </c>
-      <c r="AS238" s="36">
-        <f>AS232-AS233-AS234-AS235-AS236-AS237</f>
-        <v/>
-      </c>
-      <c r="AT238" s="36">
-        <f>AT232-AT233-AT234-AT235-AT236-AT237</f>
-        <v/>
-      </c>
-      <c r="AU238" s="36">
-        <f>AU232-AU233-AU234-AU235-AU236-AU237</f>
-        <v/>
-      </c>
-      <c r="AV238" s="36">
-        <f>AV232-AV233-AV234-AV235-AV236-AV237</f>
-        <v/>
-      </c>
-      <c r="AW238" s="36">
-        <f>AW232-AW233-AW234-AW235-AW236-AW237</f>
-        <v/>
-      </c>
-      <c r="AX238" s="36">
-        <f>AX232-AX233-AX234-AX235-AX236-AX237</f>
-        <v/>
-      </c>
-      <c r="AY238" s="36">
-        <f>AY232-AY233-AY234-AY235-AY236-AY237</f>
-        <v/>
-      </c>
-      <c r="AZ238" s="36">
-        <f>AZ232-AZ233-AZ234-AZ235-AZ236-AZ237</f>
-        <v/>
-      </c>
-      <c r="BA238" s="36">
-        <f>BA232-BA233-BA234-BA235-BA236-BA237</f>
-        <v/>
-      </c>
-      <c r="BB238" s="36">
-        <f>BB232-BB233-BB234-BB235-BB236-BB237</f>
-        <v/>
-      </c>
-      <c r="BC238" s="36">
-        <f>BC232-BC233-BC234-BC235-BC236-BC237</f>
-        <v/>
-      </c>
-      <c r="BD238" s="36">
-        <f>BD232-BD233-BD234-BD235-BD236-BD237</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="22" t="inlineStr">
+      <c r="E239" s="36">
+        <f>E233-E234-E235-E236-E237-E238</f>
+        <v/>
+      </c>
+      <c r="F239" s="36">
+        <f>F233-F234-F235-F236-F237-F238</f>
+        <v/>
+      </c>
+      <c r="G239" s="36">
+        <f>G233-G234-G235-G236-G237-G238</f>
+        <v/>
+      </c>
+      <c r="H239" s="36">
+        <f>H233-H234-H235-H236-H237-H238</f>
+        <v/>
+      </c>
+      <c r="I239" s="36">
+        <f>I233-I234-I235-I236-I237-I238</f>
+        <v/>
+      </c>
+      <c r="J239" s="36">
+        <f>J233-J234-J235-J236-J237-J238</f>
+        <v/>
+      </c>
+      <c r="K239" s="36">
+        <f>K233-K234-K235-K236-K237-K238</f>
+        <v/>
+      </c>
+      <c r="L239" s="36">
+        <f>L233-L234-L235-L236-L237-L238</f>
+        <v/>
+      </c>
+      <c r="M239" s="36">
+        <f>M233-M234-M235-M236-M237-M238</f>
+        <v/>
+      </c>
+      <c r="N239" s="36">
+        <f>N233-N234-N235-N236-N237-N238</f>
+        <v/>
+      </c>
+      <c r="O239" s="36">
+        <f>O233-O234-O235-O236-O237-O238</f>
+        <v/>
+      </c>
+      <c r="P239" s="36">
+        <f>P233-P234-P235-P236-P237-P238</f>
+        <v/>
+      </c>
+      <c r="Q239" s="36">
+        <f>Q233-Q234-Q235-Q236-Q237-Q238</f>
+        <v/>
+      </c>
+      <c r="R239" s="36">
+        <f>R233-R234-R235-R236-R237-R238</f>
+        <v/>
+      </c>
+      <c r="S239" s="36">
+        <f>S233-S234-S235-S236-S237-S238</f>
+        <v/>
+      </c>
+      <c r="T239" s="36">
+        <f>T233-T234-T235-T236-T237-T238</f>
+        <v/>
+      </c>
+      <c r="U239" s="36">
+        <f>U233-U234-U235-U236-U237-U238</f>
+        <v/>
+      </c>
+      <c r="V239" s="36">
+        <f>V233-V234-V235-V236-V237-V238</f>
+        <v/>
+      </c>
+      <c r="W239" s="36">
+        <f>W233-W234-W235-W236-W237-W238</f>
+        <v/>
+      </c>
+      <c r="X239" s="36">
+        <f>X233-X234-X235-X236-X237-X238</f>
+        <v/>
+      </c>
+      <c r="Y239" s="36">
+        <f>Y233-Y234-Y235-Y236-Y237-Y238</f>
+        <v/>
+      </c>
+      <c r="Z239" s="36">
+        <f>Z233-Z234-Z235-Z236-Z237-Z238</f>
+        <v/>
+      </c>
+      <c r="AA239" s="36">
+        <f>AA233-AA234-AA235-AA236-AA237-AA238</f>
+        <v/>
+      </c>
+      <c r="AB239" s="36">
+        <f>AB233-AB234-AB235-AB236-AB237-AB238</f>
+        <v/>
+      </c>
+      <c r="AC239" s="36">
+        <f>AC233-AC234-AC235-AC236-AC237-AC238</f>
+        <v/>
+      </c>
+      <c r="AD239" s="36">
+        <f>AD233-AD234-AD235-AD236-AD237-AD238</f>
+        <v/>
+      </c>
+      <c r="AE239" s="36">
+        <f>AE233-AE234-AE235-AE236-AE237-AE238</f>
+        <v/>
+      </c>
+      <c r="AF239" s="36">
+        <f>AF233-AF234-AF235-AF236-AF237-AF238</f>
+        <v/>
+      </c>
+      <c r="AG239" s="36">
+        <f>AG233-AG234-AG235-AG236-AG237-AG238</f>
+        <v/>
+      </c>
+      <c r="AH239" s="36">
+        <f>AH233-AH234-AH235-AH236-AH237-AH238</f>
+        <v/>
+      </c>
+      <c r="AI239" s="36">
+        <f>AI233-AI234-AI235-AI236-AI237-AI238</f>
+        <v/>
+      </c>
+      <c r="AJ239" s="36">
+        <f>AJ233-AJ234-AJ235-AJ236-AJ237-AJ238</f>
+        <v/>
+      </c>
+      <c r="AK239" s="36">
+        <f>AK233-AK234-AK235-AK236-AK237-AK238</f>
+        <v/>
+      </c>
+      <c r="AL239" s="36">
+        <f>AL233-AL234-AL235-AL236-AL237-AL238</f>
+        <v/>
+      </c>
+      <c r="AM239" s="36">
+        <f>AM233-AM234-AM235-AM236-AM237-AM238</f>
+        <v/>
+      </c>
+      <c r="AN239" s="36">
+        <f>AN233-AN234-AN235-AN236-AN237-AN238</f>
+        <v/>
+      </c>
+      <c r="AO239" s="36">
+        <f>AO233-AO234-AO235-AO236-AO237-AO238</f>
+        <v/>
+      </c>
+      <c r="AP239" s="36">
+        <f>AP233-AP234-AP235-AP236-AP237-AP238</f>
+        <v/>
+      </c>
+      <c r="AQ239" s="36">
+        <f>AQ233-AQ234-AQ235-AQ236-AQ237-AQ238</f>
+        <v/>
+      </c>
+      <c r="AR239" s="36">
+        <f>AR233-AR234-AR235-AR236-AR237-AR238</f>
+        <v/>
+      </c>
+      <c r="AS239" s="36">
+        <f>AS233-AS234-AS235-AS236-AS237-AS238</f>
+        <v/>
+      </c>
+      <c r="AT239" s="36">
+        <f>AT233-AT234-AT235-AT236-AT237-AT238</f>
+        <v/>
+      </c>
+      <c r="AU239" s="36">
+        <f>AU233-AU234-AU235-AU236-AU237-AU238</f>
+        <v/>
+      </c>
+      <c r="AV239" s="36">
+        <f>AV233-AV234-AV235-AV236-AV237-AV238</f>
+        <v/>
+      </c>
+      <c r="AW239" s="36">
+        <f>AW233-AW234-AW235-AW236-AW237-AW238</f>
+        <v/>
+      </c>
+      <c r="AX239" s="36">
+        <f>AX233-AX234-AX235-AX236-AX237-AX238</f>
+        <v/>
+      </c>
+      <c r="AY239" s="36">
+        <f>AY233-AY234-AY235-AY236-AY237-AY238</f>
+        <v/>
+      </c>
+      <c r="AZ239" s="36">
+        <f>AZ233-AZ234-AZ235-AZ236-AZ237-AZ238</f>
+        <v/>
+      </c>
+      <c r="BA239" s="36">
+        <f>BA233-BA234-BA235-BA236-BA237-BA238</f>
+        <v/>
+      </c>
+      <c r="BB239" s="36">
+        <f>BB233-BB234-BB235-BB236-BB237-BB238</f>
+        <v/>
+      </c>
+      <c r="BC239" s="36">
+        <f>BC233-BC234-BC235-BC236-BC237-BC238</f>
+        <v/>
+      </c>
+      <c r="BD239" s="36">
+        <f>BD233-BD234-BD235-BD236-BD237-BD238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B240" s="33" t="inlineStr">
+      <c r="B241" s="33" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E240" s="25" t="n">
+      <c r="E241" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F240" s="25" t="n">
+      <c r="F241" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G240" s="25" t="n">
+      <c r="G241" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H240" s="25" t="n">
+      <c r="H241" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I240" s="25" t="n">
+      <c r="I241" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J240" s="25" t="n">
+      <c r="J241" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="K240" s="25" t="n">
+      <c r="K241" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="L240" s="25" t="n">
+      <c r="L241" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="M240" s="25" t="n">
+      <c r="M241" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="N240" s="25" t="n">
+      <c r="N241" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="O240" s="25" t="n">
+      <c r="O241" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="P240" s="25" t="n">
+      <c r="P241" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="Q240" s="25" t="n">
+      <c r="Q241" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="R240" s="25" t="n">
+      <c r="R241" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="S240" s="25" t="n">
+      <c r="S241" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="T240" s="25" t="n">
+      <c r="T241" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="U240" s="25" t="n">
+      <c r="U241" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="V240" s="25" t="n">
+      <c r="V241" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="W240" s="25" t="n">
+      <c r="W241" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="X240" s="25" t="n">
+      <c r="X241" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="Y240" s="25" t="n">
+      <c r="Y241" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="Z240" s="25" t="n">
+      <c r="Z241" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="AA240" s="25" t="n">
+      <c r="AA241" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="AB240" s="25" t="n">
+      <c r="AB241" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="AC240" s="25" t="n">
+      <c r="AC241" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="AD240" s="25" t="n">
+      <c r="AD241" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="AE240" s="25" t="n">
+      <c r="AE241" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="AF240" s="25" t="n">
+      <c r="AF241" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="AG240" s="25" t="n">
+      <c r="AG241" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="AH240" s="25" t="n">
+      <c r="AH241" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="AI240" s="25" t="n">
+      <c r="AI241" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="AJ240" s="25" t="n">
+      <c r="AJ241" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="AK240" s="25" t="n">
+      <c r="AK241" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="AL240" s="25" t="n">
+      <c r="AL241" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="AM240" s="25" t="n">
+      <c r="AM241" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="AN240" s="25" t="n">
+      <c r="AN241" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="AO240" s="25" t="n">
+      <c r="AO241" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="AP240" s="25" t="n">
+      <c r="AP241" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="AQ240" s="25" t="n">
+      <c r="AQ241" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="AR240" s="25" t="n">
+      <c r="AR241" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="AS240" s="25" t="n">
+      <c r="AS241" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="AT240" s="25" t="n">
+      <c r="AT241" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="AU240" s="25" t="n">
+      <c r="AU241" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="AV240" s="25" t="n">
+      <c r="AV241" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="AW240" s="25" t="n">
+      <c r="AW241" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="AX240" s="25" t="n">
+      <c r="AX241" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="AY240" s="25" t="n">
+      <c r="AY241" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="AZ240" s="25" t="n">
+      <c r="AZ241" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="BA240" s="25" t="n">
+      <c r="BA241" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="BB240" s="25" t="n">
+      <c r="BB241" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="BC240" s="25" t="n">
+      <c r="BC241" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="BD240" s="25" t="n">
+      <c r="BD241" s="25" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="23" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="23" t="inlineStr">
         <is>
           <t>CASH IN THE BANK</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E241" s="40">
-        <f>$B$226+E238</f>
-        <v/>
-      </c>
-      <c r="F241" s="40">
-        <f>E241+F238</f>
-        <v/>
-      </c>
-      <c r="G241" s="40">
-        <f>F241+G238</f>
-        <v/>
-      </c>
-      <c r="H241" s="40">
-        <f>G241+H238</f>
-        <v/>
-      </c>
-      <c r="I241" s="40">
-        <f>H241+I238</f>
-        <v/>
-      </c>
-      <c r="J241" s="40">
-        <f>I241+J238</f>
-        <v/>
-      </c>
-      <c r="K241" s="40">
-        <f>J241+K238</f>
-        <v/>
-      </c>
-      <c r="L241" s="40">
-        <f>K241+L238</f>
-        <v/>
-      </c>
-      <c r="M241" s="40">
-        <f>L241+M238</f>
-        <v/>
-      </c>
-      <c r="N241" s="40">
-        <f>M241+N238</f>
-        <v/>
-      </c>
-      <c r="O241" s="40">
-        <f>N241+O238</f>
-        <v/>
-      </c>
-      <c r="P241" s="40">
-        <f>O241+P238</f>
-        <v/>
-      </c>
-      <c r="Q241" s="40">
-        <f>P241+Q238</f>
-        <v/>
-      </c>
-      <c r="R241" s="40">
-        <f>Q241+R238</f>
-        <v/>
-      </c>
-      <c r="S241" s="40">
-        <f>R241+S238</f>
-        <v/>
-      </c>
-      <c r="T241" s="40">
-        <f>S241+T238</f>
-        <v/>
-      </c>
-      <c r="U241" s="40">
-        <f>T241+U238</f>
-        <v/>
-      </c>
-      <c r="V241" s="40">
-        <f>U241+V238</f>
-        <v/>
-      </c>
-      <c r="W241" s="40">
-        <f>V241+W238</f>
-        <v/>
-      </c>
-      <c r="X241" s="40">
-        <f>W241+X238</f>
-        <v/>
-      </c>
-      <c r="Y241" s="40">
-        <f>X241+Y238</f>
-        <v/>
-      </c>
-      <c r="Z241" s="40">
-        <f>Y241+Z238</f>
-        <v/>
-      </c>
-      <c r="AA241" s="40">
-        <f>Z241+AA238</f>
-        <v/>
-      </c>
-      <c r="AB241" s="40">
-        <f>AA241+AB238</f>
-        <v/>
-      </c>
-      <c r="AC241" s="40">
-        <f>AB241+AC238</f>
-        <v/>
-      </c>
-      <c r="AD241" s="40">
-        <f>AC241+AD238</f>
-        <v/>
-      </c>
-      <c r="AE241" s="40">
-        <f>AD241+AE238</f>
-        <v/>
-      </c>
-      <c r="AF241" s="40">
-        <f>AE241+AF238</f>
-        <v/>
-      </c>
-      <c r="AG241" s="40">
-        <f>AF241+AG238</f>
-        <v/>
-      </c>
-      <c r="AH241" s="40">
-        <f>AG241+AH238</f>
-        <v/>
-      </c>
-      <c r="AI241" s="40">
-        <f>AH241+AI238</f>
-        <v/>
-      </c>
-      <c r="AJ241" s="40">
-        <f>AI241+AJ238</f>
-        <v/>
-      </c>
-      <c r="AK241" s="40">
-        <f>AJ241+AK238</f>
-        <v/>
-      </c>
-      <c r="AL241" s="40">
-        <f>AK241+AL238</f>
-        <v/>
-      </c>
-      <c r="AM241" s="40">
-        <f>AL241+AM238</f>
-        <v/>
-      </c>
-      <c r="AN241" s="40">
-        <f>AM241+AN238</f>
-        <v/>
-      </c>
-      <c r="AO241" s="40">
-        <f>AN241+AO238</f>
-        <v/>
-      </c>
-      <c r="AP241" s="40">
-        <f>AO241+AP238</f>
-        <v/>
-      </c>
-      <c r="AQ241" s="40">
-        <f>AP241+AQ238</f>
-        <v/>
-      </c>
-      <c r="AR241" s="40">
-        <f>AQ241+AR238</f>
-        <v/>
-      </c>
-      <c r="AS241" s="40">
-        <f>AR241+AS238</f>
-        <v/>
-      </c>
-      <c r="AT241" s="40">
-        <f>AS241+AT238</f>
-        <v/>
-      </c>
-      <c r="AU241" s="40">
-        <f>AT241+AU238</f>
-        <v/>
-      </c>
-      <c r="AV241" s="40">
-        <f>AU241+AV238</f>
-        <v/>
-      </c>
-      <c r="AW241" s="40">
-        <f>AV241+AW238</f>
-        <v/>
-      </c>
-      <c r="AX241" s="40">
-        <f>AW241+AX238</f>
-        <v/>
-      </c>
-      <c r="AY241" s="40">
-        <f>AX241+AY238</f>
-        <v/>
-      </c>
-      <c r="AZ241" s="40">
-        <f>AY241+AZ238</f>
-        <v/>
-      </c>
-      <c r="BA241" s="40">
-        <f>AZ241+BA238</f>
-        <v/>
-      </c>
-      <c r="BB241" s="40">
-        <f>BA241+BB238</f>
-        <v/>
-      </c>
-      <c r="BC241" s="40">
-        <f>BB241+BC238</f>
-        <v/>
-      </c>
-      <c r="BD241" s="40">
-        <f>BC241+BD238</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="E242" s="35" t="inlineStr">
+      <c r="E242" s="40">
+        <f>$B$226+E239</f>
+        <v/>
+      </c>
+      <c r="F242" s="40">
+        <f>E242+F239</f>
+        <v/>
+      </c>
+      <c r="G242" s="40">
+        <f>F242+G239</f>
+        <v/>
+      </c>
+      <c r="H242" s="40">
+        <f>G242+H239</f>
+        <v/>
+      </c>
+      <c r="I242" s="40">
+        <f>H242+I239</f>
+        <v/>
+      </c>
+      <c r="J242" s="40">
+        <f>I242+J239</f>
+        <v/>
+      </c>
+      <c r="K242" s="40">
+        <f>J242+K239</f>
+        <v/>
+      </c>
+      <c r="L242" s="40">
+        <f>K242+L239</f>
+        <v/>
+      </c>
+      <c r="M242" s="40">
+        <f>L242+M239</f>
+        <v/>
+      </c>
+      <c r="N242" s="40">
+        <f>M242+N239</f>
+        <v/>
+      </c>
+      <c r="O242" s="40">
+        <f>N242+O239</f>
+        <v/>
+      </c>
+      <c r="P242" s="40">
+        <f>O242+P239</f>
+        <v/>
+      </c>
+      <c r="Q242" s="40">
+        <f>P242+Q239</f>
+        <v/>
+      </c>
+      <c r="R242" s="40">
+        <f>Q242+R239</f>
+        <v/>
+      </c>
+      <c r="S242" s="40">
+        <f>R242+S239</f>
+        <v/>
+      </c>
+      <c r="T242" s="40">
+        <f>S242+T239</f>
+        <v/>
+      </c>
+      <c r="U242" s="40">
+        <f>T242+U239</f>
+        <v/>
+      </c>
+      <c r="V242" s="40">
+        <f>U242+V239</f>
+        <v/>
+      </c>
+      <c r="W242" s="40">
+        <f>V242+W239</f>
+        <v/>
+      </c>
+      <c r="X242" s="40">
+        <f>W242+X239</f>
+        <v/>
+      </c>
+      <c r="Y242" s="40">
+        <f>X242+Y239</f>
+        <v/>
+      </c>
+      <c r="Z242" s="40">
+        <f>Y242+Z239</f>
+        <v/>
+      </c>
+      <c r="AA242" s="40">
+        <f>Z242+AA239</f>
+        <v/>
+      </c>
+      <c r="AB242" s="40">
+        <f>AA242+AB239</f>
+        <v/>
+      </c>
+      <c r="AC242" s="40">
+        <f>AB242+AC239</f>
+        <v/>
+      </c>
+      <c r="AD242" s="40">
+        <f>AC242+AD239</f>
+        <v/>
+      </c>
+      <c r="AE242" s="40">
+        <f>AD242+AE239</f>
+        <v/>
+      </c>
+      <c r="AF242" s="40">
+        <f>AE242+AF239</f>
+        <v/>
+      </c>
+      <c r="AG242" s="40">
+        <f>AF242+AG239</f>
+        <v/>
+      </c>
+      <c r="AH242" s="40">
+        <f>AG242+AH239</f>
+        <v/>
+      </c>
+      <c r="AI242" s="40">
+        <f>AH242+AI239</f>
+        <v/>
+      </c>
+      <c r="AJ242" s="40">
+        <f>AI242+AJ239</f>
+        <v/>
+      </c>
+      <c r="AK242" s="40">
+        <f>AJ242+AK239</f>
+        <v/>
+      </c>
+      <c r="AL242" s="40">
+        <f>AK242+AL239</f>
+        <v/>
+      </c>
+      <c r="AM242" s="40">
+        <f>AL242+AM239</f>
+        <v/>
+      </c>
+      <c r="AN242" s="40">
+        <f>AM242+AN239</f>
+        <v/>
+      </c>
+      <c r="AO242" s="40">
+        <f>AN242+AO239</f>
+        <v/>
+      </c>
+      <c r="AP242" s="40">
+        <f>AO242+AP239</f>
+        <v/>
+      </c>
+      <c r="AQ242" s="40">
+        <f>AP242+AQ239</f>
+        <v/>
+      </c>
+      <c r="AR242" s="40">
+        <f>AQ242+AR239</f>
+        <v/>
+      </c>
+      <c r="AS242" s="40">
+        <f>AR242+AS239</f>
+        <v/>
+      </c>
+      <c r="AT242" s="40">
+        <f>AS242+AT239</f>
+        <v/>
+      </c>
+      <c r="AU242" s="40">
+        <f>AT242+AU239</f>
+        <v/>
+      </c>
+      <c r="AV242" s="40">
+        <f>AU242+AV239</f>
+        <v/>
+      </c>
+      <c r="AW242" s="40">
+        <f>AV242+AW239</f>
+        <v/>
+      </c>
+      <c r="AX242" s="40">
+        <f>AW242+AX239</f>
+        <v/>
+      </c>
+      <c r="AY242" s="40">
+        <f>AX242+AY239</f>
+        <v/>
+      </c>
+      <c r="AZ242" s="40">
+        <f>AY242+AZ239</f>
+        <v/>
+      </c>
+      <c r="BA242" s="40">
+        <f>AZ242+BA239</f>
+        <v/>
+      </c>
+      <c r="BB242" s="40">
+        <f>BA242+BB239</f>
+        <v/>
+      </c>
+      <c r="BC242" s="40">
+        <f>BB242+BC239</f>
+        <v/>
+      </c>
+      <c r="BD242" s="40">
+        <f>BC242+BD239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="E243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="F242" s="35" t="inlineStr">
+      <c r="F243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="G242" s="35" t="inlineStr">
+      <c r="G243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="H242" s="35" t="inlineStr">
+      <c r="H243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="I242" s="35" t="inlineStr">
+      <c r="I243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="J242" s="35" t="inlineStr">
+      <c r="J243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="K242" s="35" t="inlineStr">
+      <c r="K243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="L242" s="35" t="inlineStr">
+      <c r="L243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="M242" s="35" t="inlineStr">
+      <c r="M243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="N242" s="35" t="inlineStr">
+      <c r="N243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="O242" s="35" t="inlineStr">
+      <c r="O243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="P242" s="35" t="inlineStr">
+      <c r="P243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="Q242" s="35" t="inlineStr">
+      <c r="Q243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="R242" s="35" t="inlineStr">
+      <c r="R243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="S242" s="35" t="inlineStr">
+      <c r="S243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="T242" s="35" t="inlineStr">
+      <c r="T243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="U242" s="35" t="inlineStr">
+      <c r="U243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="V242" s="35" t="inlineStr">
+      <c r="V243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="W242" s="35" t="inlineStr">
+      <c r="W243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="X242" s="35" t="inlineStr">
+      <c r="X243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="Y242" s="35" t="inlineStr">
+      <c r="Y243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="Z242" s="35" t="inlineStr">
+      <c r="Z243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AA242" s="35" t="inlineStr">
+      <c r="AA243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AB242" s="35" t="inlineStr">
+      <c r="AB243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AC242" s="35" t="inlineStr">
+      <c r="AC243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AD242" s="35" t="inlineStr">
+      <c r="AD243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AE242" s="35" t="inlineStr">
+      <c r="AE243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AF242" s="35" t="inlineStr">
+      <c r="AF243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AG242" s="35" t="inlineStr">
+      <c r="AG243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AH242" s="35" t="inlineStr">
+      <c r="AH243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AI242" s="35" t="inlineStr">
+      <c r="AI243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AJ242" s="35" t="inlineStr">
+      <c r="AJ243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AK242" s="35" t="inlineStr">
+      <c r="AK243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AL242" s="35" t="inlineStr">
+      <c r="AL243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AM242" s="35" t="inlineStr">
+      <c r="AM243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AN242" s="35" t="inlineStr">
+      <c r="AN243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AO242" s="35" t="inlineStr">
+      <c r="AO243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AP242" s="35" t="inlineStr">
+      <c r="AP243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AQ242" s="35" t="inlineStr">
+      <c r="AQ243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AR242" s="35" t="inlineStr">
+      <c r="AR243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AS242" s="35" t="inlineStr">
+      <c r="AS243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AT242" s="35" t="inlineStr">
+      <c r="AT243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AU242" s="35" t="inlineStr">
+      <c r="AU243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AV242" s="35" t="inlineStr">
+      <c r="AV243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AW242" s="35" t="inlineStr">
+      <c r="AW243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AX242" s="35" t="inlineStr">
+      <c r="AX243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AY242" s="35" t="inlineStr">
+      <c r="AY243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="AZ242" s="35" t="inlineStr">
+      <c r="AZ243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="BA242" s="35" t="inlineStr">
+      <c r="BA243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="BB242" s="35" t="inlineStr">
+      <c r="BB243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="BC242" s="35" t="inlineStr">
+      <c r="BC243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="BD242" s="35" t="inlineStr">
+      <c r="BD243" s="35" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="4" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  floor</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E243" s="36">
+      <c r="E244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="F243" s="36">
+      <c r="F244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="G243" s="36">
+      <c r="G244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="H243" s="36">
+      <c r="H244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="I243" s="36">
+      <c r="I244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="J243" s="36">
+      <c r="J244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="K243" s="36">
+      <c r="K244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="L243" s="36">
+      <c r="L244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="M243" s="36">
+      <c r="M244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="N243" s="36">
+      <c r="N244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="O243" s="36">
+      <c r="O244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="P243" s="36">
+      <c r="P244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="Q243" s="36">
+      <c r="Q244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="R243" s="36">
+      <c r="R244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="S243" s="36">
+      <c r="S244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="T243" s="36">
+      <c r="T244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="U243" s="36">
+      <c r="U244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="V243" s="36">
+      <c r="V244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="W243" s="36">
+      <c r="W244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="X243" s="36">
+      <c r="X244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="Y243" s="36">
+      <c r="Y244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="Z243" s="36">
+      <c r="Z244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AA243" s="36">
+      <c r="AA244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AB243" s="36">
+      <c r="AB244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AC243" s="36">
+      <c r="AC244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AD243" s="36">
+      <c r="AD244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AE243" s="36">
+      <c r="AE244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AF243" s="36">
+      <c r="AF244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AG243" s="36">
+      <c r="AG244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AH243" s="36">
+      <c r="AH244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AI243" s="36">
+      <c r="AI244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AJ243" s="36">
+      <c r="AJ244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AK243" s="36">
+      <c r="AK244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AL243" s="36">
+      <c r="AL244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AM243" s="36">
+      <c r="AM244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AN243" s="36">
+      <c r="AN244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AO243" s="36">
+      <c r="AO244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AP243" s="36">
+      <c r="AP244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AQ243" s="36">
+      <c r="AQ244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AR243" s="36">
+      <c r="AR244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AS243" s="36">
+      <c r="AS244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AT243" s="36">
+      <c r="AT244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AU243" s="36">
+      <c r="AU244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AV243" s="36">
+      <c r="AV244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AW243" s="36">
+      <c r="AW244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AX243" s="36">
+      <c r="AX244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AY243" s="36">
+      <c r="AY244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="AZ243" s="36">
+      <c r="AZ244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="BA243" s="36">
+      <c r="BA244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="BB243" s="36">
+      <c r="BB244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="BC243" s="36">
+      <c r="BC244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
-      <c r="BD243" s="36">
+      <c r="BD244" s="36">
         <f>-$B$227</f>
         <v/>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="27" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  headroom</t>
         </is>
       </c>
-      <c r="E244" s="36">
-        <f>E241-E243</f>
-        <v/>
-      </c>
-      <c r="F244" s="36">
-        <f>F241-F243</f>
-        <v/>
-      </c>
-      <c r="G244" s="36">
-        <f>G241-G243</f>
-        <v/>
-      </c>
-      <c r="H244" s="36">
-        <f>H241-H243</f>
-        <v/>
-      </c>
-      <c r="I244" s="36">
-        <f>I241-I243</f>
-        <v/>
-      </c>
-      <c r="J244" s="36">
-        <f>J241-J243</f>
-        <v/>
-      </c>
-      <c r="K244" s="36">
-        <f>K241-K243</f>
-        <v/>
-      </c>
-      <c r="L244" s="36">
-        <f>L241-L243</f>
-        <v/>
-      </c>
-      <c r="M244" s="36">
-        <f>M241-M243</f>
-        <v/>
-      </c>
-      <c r="N244" s="36">
-        <f>N241-N243</f>
-        <v/>
-      </c>
-      <c r="O244" s="36">
-        <f>O241-O243</f>
-        <v/>
-      </c>
-      <c r="P244" s="36">
-        <f>P241-P243</f>
-        <v/>
-      </c>
-      <c r="Q244" s="36">
-        <f>Q241-Q243</f>
-        <v/>
-      </c>
-      <c r="R244" s="36">
-        <f>R241-R243</f>
-        <v/>
-      </c>
-      <c r="S244" s="36">
-        <f>S241-S243</f>
-        <v/>
-      </c>
-      <c r="T244" s="36">
-        <f>T241-T243</f>
-        <v/>
-      </c>
-      <c r="U244" s="36">
-        <f>U241-U243</f>
-        <v/>
-      </c>
-      <c r="V244" s="36">
-        <f>V241-V243</f>
-        <v/>
-      </c>
-      <c r="W244" s="36">
-        <f>W241-W243</f>
-        <v/>
-      </c>
-      <c r="X244" s="36">
-        <f>X241-X243</f>
-        <v/>
-      </c>
-      <c r="Y244" s="36">
-        <f>Y241-Y243</f>
-        <v/>
-      </c>
-      <c r="Z244" s="36">
-        <f>Z241-Z243</f>
-        <v/>
-      </c>
-      <c r="AA244" s="36">
-        <f>AA241-AA243</f>
-        <v/>
-      </c>
-      <c r="AB244" s="36">
-        <f>AB241-AB243</f>
-        <v/>
-      </c>
-      <c r="AC244" s="36">
-        <f>AC241-AC243</f>
-        <v/>
-      </c>
-      <c r="AD244" s="36">
-        <f>AD241-AD243</f>
-        <v/>
-      </c>
-      <c r="AE244" s="36">
-        <f>AE241-AE243</f>
-        <v/>
-      </c>
-      <c r="AF244" s="36">
-        <f>AF241-AF243</f>
-        <v/>
-      </c>
-      <c r="AG244" s="36">
-        <f>AG241-AG243</f>
-        <v/>
-      </c>
-      <c r="AH244" s="36">
-        <f>AH241-AH243</f>
-        <v/>
-      </c>
-      <c r="AI244" s="36">
-        <f>AI241-AI243</f>
-        <v/>
-      </c>
-      <c r="AJ244" s="36">
-        <f>AJ241-AJ243</f>
-        <v/>
-      </c>
-      <c r="AK244" s="36">
-        <f>AK241-AK243</f>
-        <v/>
-      </c>
-      <c r="AL244" s="36">
-        <f>AL241-AL243</f>
-        <v/>
-      </c>
-      <c r="AM244" s="36">
-        <f>AM241-AM243</f>
-        <v/>
-      </c>
-      <c r="AN244" s="36">
-        <f>AN241-AN243</f>
-        <v/>
-      </c>
-      <c r="AO244" s="36">
-        <f>AO241-AO243</f>
-        <v/>
-      </c>
-      <c r="AP244" s="36">
-        <f>AP241-AP243</f>
-        <v/>
-      </c>
-      <c r="AQ244" s="36">
-        <f>AQ241-AQ243</f>
-        <v/>
-      </c>
-      <c r="AR244" s="36">
-        <f>AR241-AR243</f>
-        <v/>
-      </c>
-      <c r="AS244" s="36">
-        <f>AS241-AS243</f>
-        <v/>
-      </c>
-      <c r="AT244" s="36">
-        <f>AT241-AT243</f>
-        <v/>
-      </c>
-      <c r="AU244" s="36">
-        <f>AU241-AU243</f>
-        <v/>
-      </c>
-      <c r="AV244" s="36">
-        <f>AV241-AV243</f>
-        <v/>
-      </c>
-      <c r="AW244" s="36">
-        <f>AW241-AW243</f>
-        <v/>
-      </c>
-      <c r="AX244" s="36">
-        <f>AX241-AX243</f>
-        <v/>
-      </c>
-      <c r="AY244" s="36">
-        <f>AY241-AY243</f>
-        <v/>
-      </c>
-      <c r="AZ244" s="36">
-        <f>AZ241-AZ243</f>
-        <v/>
-      </c>
-      <c r="BA244" s="36">
-        <f>BA241-BA243</f>
-        <v/>
-      </c>
-      <c r="BB244" s="36">
-        <f>BB241-BB243</f>
-        <v/>
-      </c>
-      <c r="BC244" s="36">
-        <f>BC241-BC243</f>
-        <v/>
-      </c>
-      <c r="BD244" s="36">
-        <f>BD241-BD243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   This is the app's C13. Cash may go NEGATIVE — that is the credit line being drawn — but never below the floor, which is the line fully drawn.</t>
-        </is>
+      <c r="E245" s="36">
+        <f>E242-E244</f>
+        <v/>
+      </c>
+      <c r="F245" s="36">
+        <f>F242-F244</f>
+        <v/>
+      </c>
+      <c r="G245" s="36">
+        <f>G242-G244</f>
+        <v/>
+      </c>
+      <c r="H245" s="36">
+        <f>H242-H244</f>
+        <v/>
+      </c>
+      <c r="I245" s="36">
+        <f>I242-I244</f>
+        <v/>
+      </c>
+      <c r="J245" s="36">
+        <f>J242-J244</f>
+        <v/>
+      </c>
+      <c r="K245" s="36">
+        <f>K242-K244</f>
+        <v/>
+      </c>
+      <c r="L245" s="36">
+        <f>L242-L244</f>
+        <v/>
+      </c>
+      <c r="M245" s="36">
+        <f>M242-M244</f>
+        <v/>
+      </c>
+      <c r="N245" s="36">
+        <f>N242-N244</f>
+        <v/>
+      </c>
+      <c r="O245" s="36">
+        <f>O242-O244</f>
+        <v/>
+      </c>
+      <c r="P245" s="36">
+        <f>P242-P244</f>
+        <v/>
+      </c>
+      <c r="Q245" s="36">
+        <f>Q242-Q244</f>
+        <v/>
+      </c>
+      <c r="R245" s="36">
+        <f>R242-R244</f>
+        <v/>
+      </c>
+      <c r="S245" s="36">
+        <f>S242-S244</f>
+        <v/>
+      </c>
+      <c r="T245" s="36">
+        <f>T242-T244</f>
+        <v/>
+      </c>
+      <c r="U245" s="36">
+        <f>U242-U244</f>
+        <v/>
+      </c>
+      <c r="V245" s="36">
+        <f>V242-V244</f>
+        <v/>
+      </c>
+      <c r="W245" s="36">
+        <f>W242-W244</f>
+        <v/>
+      </c>
+      <c r="X245" s="36">
+        <f>X242-X244</f>
+        <v/>
+      </c>
+      <c r="Y245" s="36">
+        <f>Y242-Y244</f>
+        <v/>
+      </c>
+      <c r="Z245" s="36">
+        <f>Z242-Z244</f>
+        <v/>
+      </c>
+      <c r="AA245" s="36">
+        <f>AA242-AA244</f>
+        <v/>
+      </c>
+      <c r="AB245" s="36">
+        <f>AB242-AB244</f>
+        <v/>
+      </c>
+      <c r="AC245" s="36">
+        <f>AC242-AC244</f>
+        <v/>
+      </c>
+      <c r="AD245" s="36">
+        <f>AD242-AD244</f>
+        <v/>
+      </c>
+      <c r="AE245" s="36">
+        <f>AE242-AE244</f>
+        <v/>
+      </c>
+      <c r="AF245" s="36">
+        <f>AF242-AF244</f>
+        <v/>
+      </c>
+      <c r="AG245" s="36">
+        <f>AG242-AG244</f>
+        <v/>
+      </c>
+      <c r="AH245" s="36">
+        <f>AH242-AH244</f>
+        <v/>
+      </c>
+      <c r="AI245" s="36">
+        <f>AI242-AI244</f>
+        <v/>
+      </c>
+      <c r="AJ245" s="36">
+        <f>AJ242-AJ244</f>
+        <v/>
+      </c>
+      <c r="AK245" s="36">
+        <f>AK242-AK244</f>
+        <v/>
+      </c>
+      <c r="AL245" s="36">
+        <f>AL242-AL244</f>
+        <v/>
+      </c>
+      <c r="AM245" s="36">
+        <f>AM242-AM244</f>
+        <v/>
+      </c>
+      <c r="AN245" s="36">
+        <f>AN242-AN244</f>
+        <v/>
+      </c>
+      <c r="AO245" s="36">
+        <f>AO242-AO244</f>
+        <v/>
+      </c>
+      <c r="AP245" s="36">
+        <f>AP242-AP244</f>
+        <v/>
+      </c>
+      <c r="AQ245" s="36">
+        <f>AQ242-AQ244</f>
+        <v/>
+      </c>
+      <c r="AR245" s="36">
+        <f>AR242-AR244</f>
+        <v/>
+      </c>
+      <c r="AS245" s="36">
+        <f>AS242-AS244</f>
+        <v/>
+      </c>
+      <c r="AT245" s="36">
+        <f>AT242-AT244</f>
+        <v/>
+      </c>
+      <c r="AU245" s="36">
+        <f>AU242-AU244</f>
+        <v/>
+      </c>
+      <c r="AV245" s="36">
+        <f>AV242-AV244</f>
+        <v/>
+      </c>
+      <c r="AW245" s="36">
+        <f>AW242-AW244</f>
+        <v/>
+      </c>
+      <c r="AX245" s="36">
+        <f>AX242-AX244</f>
+        <v/>
+      </c>
+      <c r="AY245" s="36">
+        <f>AY242-AY244</f>
+        <v/>
+      </c>
+      <c r="AZ245" s="36">
+        <f>AZ242-AZ244</f>
+        <v/>
+      </c>
+      <c r="BA245" s="36">
+        <f>BA242-BA244</f>
+        <v/>
+      </c>
+      <c r="BB245" s="36">
+        <f>BB242-BB244</f>
+        <v/>
+      </c>
+      <c r="BC245" s="36">
+        <f>BC242-BC244</f>
+        <v/>
+      </c>
+      <c r="BD245" s="36">
+        <f>BD242-BD244</f>
+        <v/>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The app states the same rule the other way round: it constrains cumulative NET FLOW (which excludes</t>
+          <t xml:space="preserve">   This is the app's C13. Cash may go NEGATIVE — that is the credit line being drawn — but never below the floor, which is the line fully drawn.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   opening cash) against -(opening + credit). Both are the same constraint; mixing them double-counts the opening balance.</t>
+          <t xml:space="preserve">   The app states the same rule the other way round: it constrains cumulative NET FLOW (which excludes</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   opening cash) against -(opening + credit). Both are the same constraint; mixing them double-counts the opening balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   ⚠️ It barely binds here, because the biggest weekly outgoing a real farm has is PAYROLL, and labour is v7. Do not read this curve as realistic yet.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="3" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
         <is>
           <t>8 — THE OPTIMIZER</t>
         </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B251" s="52">
-        <f>SUM(E135:BD135)*$I$18+SUM(E141:BD141)*$I$19+SUM(E162:BD162)*$I$20+SUM(E170:BD170)*$I$21+SUM(E191:BD191)*$I$22+SUM(E197:BD197)*$I$23</f>
-        <v/>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>Growing cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B252" s="52">
-        <f>SUM(E234:BD234)</f>
-        <v/>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>seed at planting + fertiliser and fuel every week in the ground</t>
-        </is>
+        <f>SUM(E135:BD135)*$I$18+SUM(E141:BD141)*$I$19+SUM(E162:BD162)*$I$20+SUM(E170:BD170)*$I$21+SUM(E191:BD191)*$I$22+SUM(E197:BD197)*$I$23</f>
+        <v/>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Growing cost</t>
         </is>
       </c>
       <c r="B253" s="52">
-        <f>SUM(E233:BD233)</f>
-        <v/>
+        <f>SUM(E235:BD235)</f>
+        <v/>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>seed at planting + fertiliser and fuel every week in the ground</t>
+        </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Fixed cost</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="B254" s="52">
-        <f>SUM(E235:BD235)</f>
-        <v/>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>owed all 52 weeks whatever you plant</t>
-        </is>
+        <f>SUM(E234:BD234)</f>
+        <v/>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Overhead</t>
+          <t>Fixed cost</t>
         </is>
       </c>
       <c r="B255" s="52">
         <f>SUM(E236:BD236)</f>
         <v/>
       </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>owed all 52 weeks whatever you plant</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Wages</t>
+          <t>Overhead</t>
         </is>
       </c>
       <c r="B256" s="52">
         <f>SUM(E237:BD237)</f>
         <v/>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="B257" s="52">
+        <f>SUM(E238:BD238)</f>
+        <v/>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>committed — owed whether or not the crops need the hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="23" t="inlineStr">
-        <is>
-          <t>PROFIT  (the objective)</t>
-        </is>
-      </c>
-      <c r="B257" s="53">
-        <f>B251-SUM(B252:B256)</f>
-        <v/>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>&lt;-- MAXIMISE THIS CELL</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
+          <t>Peak borrowing</t>
+        </is>
+      </c>
+      <c r="B258" s="52">
+        <f>MAX(0,-MIN(E242:BD242))</f>
+        <v/>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>the deepest the credit line is ever drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="B259" s="52">
+        <f>$B$230*SUMPRODUCT((E242:BD242&lt;0)*-E242:BD242)/52</f>
+        <v/>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>APR x the AVERAGE amount borrowed — the app's own post-solve formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠️ Reported, NOT optimised over. The plan is chosen first and the borrowing it implies is priced afterwards,</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     so the solver has no reason to shift sales earlier to borrow less. That is the app's simplification, inherited on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="23" t="inlineStr">
+        <is>
+          <t>PROFIT  (the objective)</t>
+        </is>
+      </c>
+      <c r="B262" s="53">
+        <f>B252-SUM(B253:B257)-B259</f>
+        <v/>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>&lt;-- MAXIMISE THIS CELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
           <t>Plantings chosen</t>
         </is>
       </c>
-      <c r="B258" s="54">
+      <c r="B263" s="54">
         <f>SUM($D$38:$D$105)</f>
         <v/>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>of 68 offered</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>Annual caps</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Kale / Wholesale — sold all year</t>
-        </is>
-      </c>
-      <c r="B261" s="36">
-        <f>SUM(E170:BD170)</f>
-        <v/>
-      </c>
-      <c r="C261" s="35" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="D261" s="36">
-        <f>$D$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>SOLVER SETUP — Tools &gt; Solver</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
-        <is>
-          <t>Target cell</t>
-        </is>
-      </c>
-      <c r="B264" s="27" t="inlineStr">
-        <is>
-          <t>$B$257</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr">
-        <is>
-          <t>set to MAXIMUM</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>By changing cells</t>
-        </is>
-      </c>
-      <c r="B265" s="27" t="inlineStr">
-        <is>
-          <t>$C$38:$D$105</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr">
-        <is>
-          <t>acres AND plant? together</t>
+          <t>Annual caps</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ...and</t>
-        </is>
-      </c>
-      <c r="B266" s="27" t="inlineStr">
-        <is>
-          <t>$E$134:$BD$134;$E$140:$BD$140;$E$161:$BD$161;$E$169:$BD$169;$E$190:$BD$190;$E$196:$BD$196</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>the OFFERED rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="27" t="inlineStr">
-        <is>
-          <t>Constraint — PLANT? is binary</t>
-        </is>
-      </c>
-      <c r="B267" s="27" t="inlineStr">
-        <is>
-          <t>$D$38:$D$105  =  Binary</t>
-        </is>
+          <t xml:space="preserve">   Kale / Wholesale — sold all year</t>
+        </is>
+      </c>
+      <c r="B266" s="36">
+        <f>SUM(E170:BD170)</f>
+        <v/>
+      </c>
+      <c r="C266" s="35" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="D266" s="36">
+        <f>$D$21</f>
+        <v/>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="27" t="inlineStr">
-        <is>
-          <t>Constraint — C9 acres &lt;= max</t>
-        </is>
-      </c>
-      <c r="B268" s="27" t="inlineStr">
-        <is>
-          <t>$C$38:$C$105  &lt;=  $BE$38:$BE$105</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>no acres without deciding to plant</t>
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>SOLVER SETUP — Tools &gt; Solver</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="27" t="inlineStr">
-        <is>
-          <t>Constraint — C10 acres &gt;= min</t>
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Target cell</t>
         </is>
       </c>
       <c r="B269" s="27" t="inlineStr">
         <is>
-          <t>$C$38:$C$105  &gt;=  $BF$38:$BF$105</t>
+          <t>$B$262</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>planted means a real block</t>
+          <t>set to MAXIMUM</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="27" t="inlineStr">
-        <is>
-          <t>Constraint — Spinach/Farmers Market sold &lt;= ceiling</t>
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>By changing cells</t>
         </is>
       </c>
       <c r="B270" s="27" t="inlineStr">
         <is>
-          <t>$E$135:$BD$135  &lt;=  $E$133:$BD$133</t>
+          <t>$C$38:$D$105</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>acres AND plant? together</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Spinach/Wholesale sold &lt;= ceiling</t>
+          <t xml:space="preserve">  ...and</t>
         </is>
       </c>
       <c r="B271" s="27" t="inlineStr">
         <is>
-          <t>$E$141:$BD$141  &lt;=  $E$139:$BD$139</t>
+          <t>$E$134:$BD$134;$E$140:$BD$140;$E$161:$BD$161;$E$169:$BD$169;$E$190:$BD$190;$E$196:$BD$196</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>the OFFERED rows</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Kale/Farmers Market sold &lt;= ceiling</t>
+          <t>Constraint — PLANT? is binary</t>
         </is>
       </c>
       <c r="B272" s="27" t="inlineStr">
         <is>
-          <t>$E$162:$BD$162  &lt;=  $E$160:$BD$160</t>
+          <t>$D$38:$D$105  =  Binary</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Kale/Wholesale sold &lt;= ceiling</t>
+          <t>Constraint — C9 acres &lt;= max</t>
         </is>
       </c>
       <c r="B273" s="27" t="inlineStr">
         <is>
-          <t>$E$170:$BD$170  &lt;=  $E$166:$BD$166</t>
+          <t>$C$38:$C$105  &lt;=  $BE$38:$BE$105</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>no acres without deciding to plant</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Garlic/Farmers Market sold &lt;= ceiling</t>
+          <t>Constraint — C10 acres &gt;= min</t>
         </is>
       </c>
       <c r="B274" s="27" t="inlineStr">
         <is>
-          <t>$E$191:$BD$191  &lt;=  $E$189:$BD$189</t>
+          <t>$C$38:$C$105  &gt;=  $BF$38:$BF$105</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>planted means a real block</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Garlic/Wholesale sold &lt;= ceiling</t>
+          <t>Constraint — Spinach/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B275" s="27" t="inlineStr">
         <is>
-          <t>$E$197:$BD$197  &lt;=  $E$195:$BD$195</t>
+          <t>$E$135:$BD$135  &lt;=  $E$133:$BD$133</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Spinach stock never negative</t>
+          <t>Constraint — Spinach/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B276" s="27" t="inlineStr">
         <is>
-          <t>$E$145:$BD$145  &gt;=  0</t>
+          <t>$E$141:$BD$141  &lt;=  $E$139:$BD$139</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Kale stock never negative</t>
+          <t>Constraint — Kale/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B277" s="27" t="inlineStr">
         <is>
-          <t>$E$174:$BD$174  &gt;=  0</t>
+          <t>$E$162:$BD$162  &lt;=  $E$160:$BD$160</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Garlic stock never negative</t>
+          <t>Constraint — Kale/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B278" s="27" t="inlineStr">
         <is>
-          <t>$E$201:$BD$201  &gt;=  0</t>
+          <t>$E$170:$BD$170  &lt;=  $E$166:$BD$166</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Spinach shelf life</t>
+          <t>Constraint — Garlic/Farmers Market sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B279" s="27" t="inlineStr">
         <is>
-          <t>$E$145:$BD$145  &lt;=  $E$148:$BD$148</t>
-        </is>
-      </c>
-      <c r="G279" s="2" t="inlineStr">
-        <is>
-          <t>nothing held longer than it keeps</t>
+          <t>$E$191:$BD$191  &lt;=  $E$189:$BD$189</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Kale shelf life</t>
+          <t>Constraint — Garlic/Wholesale sold &lt;= ceiling</t>
         </is>
       </c>
       <c r="B280" s="27" t="inlineStr">
         <is>
-          <t>$E$174:$BD$174  &lt;=  $E$177:$BD$177</t>
-        </is>
-      </c>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>nothing held longer than it keeps</t>
+          <t>$E$197:$BD$197  &lt;=  $E$195:$BD$195</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="27" t="inlineStr">
         <is>
-          <t>Constraint — Garlic shelf life</t>
+          <t>Constraint — Spinach stock never negative</t>
         </is>
       </c>
       <c r="B281" s="27" t="inlineStr">
         <is>
-          <t>$E$201:$BD$201  &lt;=  $E$204:$BD$204</t>
-        </is>
-      </c>
-      <c r="G281" s="2" t="inlineStr">
-        <is>
-          <t>nothing held longer than it keeps</t>
+          <t>$E$145:$BD$145  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="27" t="inlineStr">
         <is>
-          <t>Constraint — cold store</t>
+          <t>Constraint — Kale stock never negative</t>
         </is>
       </c>
       <c r="B282" s="27" t="inlineStr">
         <is>
-          <t>$E$212:$BD$212  &lt;=  $B$6</t>
+          <t>$E$174:$BD$174  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="27" t="inlineStr">
         <is>
-          <t>Constraint — ambient store</t>
+          <t>Constraint — Garlic stock never negative</t>
         </is>
       </c>
       <c r="B283" s="27" t="inlineStr">
         <is>
-          <t>$E$219:$BD$219  &lt;=  $B$7</t>
+          <t>$E$201:$BD$201  &gt;=  0</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="27" t="inlineStr">
         <is>
-          <t>Constraint — land</t>
+          <t>Constraint — Spinach shelf life</t>
         </is>
       </c>
       <c r="B284" s="27" t="inlineStr">
         <is>
-          <t>$E$109:$BD$109  &lt;=  $B$5</t>
+          <t>$E$145:$BD$145  &lt;=  $E$148:$BD$148</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>nothing held longer than it keeps</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="27" t="inlineStr">
         <is>
-          <t>Constraint — CROP HOURS &lt;= crew</t>
+          <t>Constraint — Kale shelf life</t>
         </is>
       </c>
       <c r="B285" s="27" t="inlineStr">
         <is>
-          <t>$E$121:$BD$121  &lt;=  $E$116:$BD$116</t>
+          <t>$E$174:$BD$174  &lt;=  $E$177:$BD$177</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>the app's C2</t>
+          <t>nothing held longer than it keeps</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="27" t="inlineStr">
         <is>
+          <t>Constraint — Garlic shelf life</t>
+        </is>
+      </c>
+      <c r="B286" s="27" t="inlineStr">
+        <is>
+          <t>$E$201:$BD$201  &lt;=  $E$204:$BD$204</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>nothing held longer than it keeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="27" t="inlineStr">
+        <is>
+          <t>Constraint — cold store</t>
+        </is>
+      </c>
+      <c r="B287" s="27" t="inlineStr">
+        <is>
+          <t>$E$212:$BD$212  &lt;=  $B$6</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="27" t="inlineStr">
+        <is>
+          <t>Constraint — ambient store</t>
+        </is>
+      </c>
+      <c r="B288" s="27" t="inlineStr">
+        <is>
+          <t>$E$219:$BD$219  &lt;=  $B$7</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="27" t="inlineStr">
+        <is>
+          <t>Constraint — land</t>
+        </is>
+      </c>
+      <c r="B289" s="27" t="inlineStr">
+        <is>
+          <t>$E$109:$BD$109  &lt;=  $B$5</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="27" t="inlineStr">
+        <is>
+          <t>Constraint — CROP HOURS &lt;= crew</t>
+        </is>
+      </c>
+      <c r="B290" s="27" t="inlineStr">
+        <is>
+          <t>$E$121:$BD$121  &lt;=  $E$116:$BD$116</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>the app's C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="27" t="inlineStr">
+        <is>
           <t>Constraint — CASH FLOOR</t>
         </is>
       </c>
-      <c r="B286" s="27" t="inlineStr">
-        <is>
-          <t>$E$241:$BD$241  &gt;=  $E$243:$BD$243</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="B291" s="27" t="inlineStr">
+        <is>
+          <t>$E$242:$BD$242  &gt;=  $E$244:$BD$244</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
         <is>
           <t>the app's C13</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="4" t="inlineStr">
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B287" s="27" t="inlineStr">
+      <c r="B292" s="27" t="inlineStr">
         <is>
           <t>engine = LibreOffice CoinMP Linear Solver</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="G292" s="2" t="inlineStr">
         <is>
           <t>tick 'Assume variables as non-negative'</t>
         </is>
@@ -31522,7 +31753,7 @@
       <formula>$B$7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E244:BD244">
+  <conditionalFormatting sqref="E245:BD245">
     <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
